--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mericles - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F1F631-3D03-4299-BC5F-61BA5E5358A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBCECB4-5D63-4EE9-9E94-08E3D0D86017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mericles - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBCECB4-5D63-4EE9-9E94-08E3D0D86017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B0F656-1375-41B4-81F8-3DDFA396A39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2573" uniqueCount="64">
   <si>
     <t>Company Name</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>Josh Gregory</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
   </si>
 </sst>
 </file>
@@ -14166,106 +14169,514 @@
       </c>
     </row>
     <row r="471" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H471" s="2"/>
-      <c r="I471" s="1"/>
+      <c r="B471" t="s">
+        <v>30</v>
+      </c>
+      <c r="C471">
+        <v>1926</v>
+      </c>
+      <c r="D471" t="s">
+        <v>31</v>
+      </c>
+      <c r="F471" t="s">
+        <v>63</v>
+      </c>
+      <c r="G471" t="s">
+        <v>13</v>
+      </c>
+      <c r="H471" s="2">
+        <v>0</v>
+      </c>
+      <c r="I471" s="1">
+        <v>46118.811805555553</v>
+      </c>
+      <c r="J471">
+        <v>1</v>
+      </c>
+      <c r="K471" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="472" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H472" s="2"/>
-      <c r="I472" s="1"/>
+      <c r="B472" t="s">
+        <v>30</v>
+      </c>
+      <c r="C472">
+        <v>1927</v>
+      </c>
+      <c r="D472" t="s">
+        <v>33</v>
+      </c>
+      <c r="F472" t="s">
+        <v>63</v>
+      </c>
+      <c r="G472" t="s">
+        <v>13</v>
+      </c>
+      <c r="H472" s="2">
+        <v>0</v>
+      </c>
+      <c r="I472" s="1">
+        <v>46118.8125</v>
+      </c>
+      <c r="J472">
+        <v>1</v>
+      </c>
+      <c r="K472" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="473" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H473" s="2"/>
-      <c r="I473" s="1"/>
+      <c r="B473" t="s">
+        <v>30</v>
+      </c>
+      <c r="C473">
+        <v>3789</v>
+      </c>
+      <c r="D473" t="s">
+        <v>60</v>
+      </c>
+      <c r="E473" t="s">
+        <v>36</v>
+      </c>
+      <c r="F473" t="s">
+        <v>63</v>
+      </c>
+      <c r="G473" t="s">
+        <v>13</v>
+      </c>
+      <c r="H473" s="2">
+        <v>0</v>
+      </c>
+      <c r="I473" s="1">
+        <v>46118.813194444447</v>
+      </c>
+      <c r="J473">
+        <v>1</v>
+      </c>
+      <c r="K473" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="474" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H474" s="2"/>
-      <c r="I474" s="1"/>
+      <c r="B474" t="s">
+        <v>30</v>
+      </c>
+      <c r="C474">
+        <v>1932</v>
+      </c>
+      <c r="D474" t="s">
+        <v>39</v>
+      </c>
+      <c r="E474" t="s">
+        <v>36</v>
+      </c>
+      <c r="F474" t="s">
+        <v>63</v>
+      </c>
+      <c r="G474" t="s">
+        <v>13</v>
+      </c>
+      <c r="H474" s="2">
+        <v>0</v>
+      </c>
+      <c r="I474" s="1">
+        <v>46118.813194444447</v>
+      </c>
+      <c r="J474">
+        <v>1</v>
+      </c>
+      <c r="K474" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="475" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H475" s="2"/>
-      <c r="I475" s="1"/>
+      <c r="B475" t="s">
+        <v>30</v>
+      </c>
+      <c r="C475">
+        <v>2977</v>
+      </c>
+      <c r="D475" t="s">
+        <v>56</v>
+      </c>
+      <c r="F475" t="s">
+        <v>63</v>
+      </c>
+      <c r="G475" t="s">
+        <v>13</v>
+      </c>
+      <c r="H475" s="2">
+        <v>0</v>
+      </c>
+      <c r="I475" s="1">
+        <v>46118.813888888886</v>
+      </c>
+      <c r="J475">
+        <v>1</v>
+      </c>
+      <c r="K475" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="476" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H476" s="2"/>
-      <c r="I476" s="1"/>
+      <c r="B476" t="s">
+        <v>30</v>
+      </c>
+      <c r="C476">
+        <v>1935</v>
+      </c>
+      <c r="D476" t="s">
+        <v>42</v>
+      </c>
+      <c r="E476" t="s">
+        <v>36</v>
+      </c>
+      <c r="F476" t="s">
+        <v>63</v>
+      </c>
+      <c r="G476" t="s">
+        <v>10</v>
+      </c>
+      <c r="H476" s="2">
+        <v>8.4375000000000006E-3</v>
+      </c>
+      <c r="I476" s="1">
+        <v>46118.813888888886</v>
+      </c>
+      <c r="J476">
+        <v>1</v>
+      </c>
+      <c r="K476" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="477" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H477" s="2"/>
-      <c r="I477" s="1"/>
+      <c r="B477" t="s">
+        <v>30</v>
+      </c>
+      <c r="C477">
+        <v>1936</v>
+      </c>
+      <c r="D477" t="s">
+        <v>43</v>
+      </c>
+      <c r="F477" t="s">
+        <v>63</v>
+      </c>
+      <c r="G477" t="s">
+        <v>13</v>
+      </c>
+      <c r="H477" s="2">
+        <v>0</v>
+      </c>
+      <c r="I477" s="1">
+        <v>46118.793171296296</v>
+      </c>
+      <c r="J477">
+        <v>0</v>
+      </c>
+      <c r="K477" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="478" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H478" s="2"/>
-      <c r="I478" s="1"/>
+      <c r="B478" t="s">
+        <v>30</v>
+      </c>
+      <c r="C478">
+        <v>3890</v>
+      </c>
+      <c r="D478" t="s">
+        <v>62</v>
+      </c>
+      <c r="E478" t="s">
+        <v>36</v>
+      </c>
+      <c r="F478" t="s">
+        <v>63</v>
+      </c>
+      <c r="G478" t="s">
+        <v>13</v>
+      </c>
+      <c r="H478" s="2">
+        <v>0</v>
+      </c>
+      <c r="I478" s="1">
+        <v>46118.793865740743</v>
+      </c>
+      <c r="J478">
+        <v>1</v>
+      </c>
+      <c r="K478" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="479" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H479" s="2"/>
-      <c r="I479" s="1"/>
+      <c r="B479" t="s">
+        <v>30</v>
+      </c>
+      <c r="C479">
+        <v>1937</v>
+      </c>
+      <c r="D479" t="s">
+        <v>44</v>
+      </c>
+      <c r="E479" t="s">
+        <v>36</v>
+      </c>
+      <c r="F479" t="s">
+        <v>63</v>
+      </c>
+      <c r="G479" t="s">
+        <v>13</v>
+      </c>
+      <c r="H479" s="2">
+        <v>0</v>
+      </c>
+      <c r="I479" s="1">
+        <v>46118.794560185182</v>
+      </c>
+      <c r="J479">
+        <v>1</v>
+      </c>
+      <c r="K479" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="480" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H480" s="2"/>
-      <c r="I480" s="1"/>
-    </row>
-    <row r="481" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H481" s="2"/>
-      <c r="I481" s="1"/>
-    </row>
-    <row r="482" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H482" s="2"/>
-      <c r="I482" s="1"/>
-    </row>
-    <row r="483" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H483" s="2"/>
-      <c r="I483" s="1"/>
-    </row>
-    <row r="484" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H484" s="2"/>
-      <c r="I484" s="1"/>
-    </row>
-    <row r="485" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H485" s="2"/>
-      <c r="I485" s="1"/>
-    </row>
-    <row r="486" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B480" t="s">
+        <v>30</v>
+      </c>
+      <c r="C480">
+        <v>3788</v>
+      </c>
+      <c r="D480" t="s">
+        <v>61</v>
+      </c>
+      <c r="E480" t="s">
+        <v>36</v>
+      </c>
+      <c r="F480" t="s">
+        <v>63</v>
+      </c>
+      <c r="G480" t="s">
+        <v>10</v>
+      </c>
+      <c r="H480" s="2">
+        <v>7.5115740740740742E-3</v>
+      </c>
+      <c r="I480" s="1">
+        <v>46118.794560185182</v>
+      </c>
+      <c r="J480">
+        <v>1</v>
+      </c>
+      <c r="K480" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="481" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B481" t="s">
+        <v>30</v>
+      </c>
+      <c r="C481">
+        <v>3868</v>
+      </c>
+      <c r="D481" t="s">
+        <v>36</v>
+      </c>
+      <c r="E481" t="s">
+        <v>36</v>
+      </c>
+      <c r="F481" t="s">
+        <v>63</v>
+      </c>
+      <c r="G481" t="s">
+        <v>13</v>
+      </c>
+      <c r="H481" s="2">
+        <v>0</v>
+      </c>
+      <c r="I481" s="1">
+        <v>46118.795254629629</v>
+      </c>
+      <c r="J481">
+        <v>1</v>
+      </c>
+      <c r="K481" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="482" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B482" t="s">
+        <v>30</v>
+      </c>
+      <c r="C482">
+        <v>1939</v>
+      </c>
+      <c r="D482" t="s">
+        <v>46</v>
+      </c>
+      <c r="E482" t="s">
+        <v>36</v>
+      </c>
+      <c r="F482" t="s">
+        <v>63</v>
+      </c>
+      <c r="G482" t="s">
+        <v>13</v>
+      </c>
+      <c r="H482" s="2">
+        <v>0</v>
+      </c>
+      <c r="I482" s="1">
+        <v>46118.795254629629</v>
+      </c>
+      <c r="J482">
+        <v>1</v>
+      </c>
+      <c r="K482" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="483" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B483" t="s">
+        <v>30</v>
+      </c>
+      <c r="C483">
+        <v>1941</v>
+      </c>
+      <c r="D483" t="s">
+        <v>48</v>
+      </c>
+      <c r="E483" t="s">
+        <v>36</v>
+      </c>
+      <c r="F483" t="s">
+        <v>63</v>
+      </c>
+      <c r="G483" t="s">
+        <v>13</v>
+      </c>
+      <c r="H483" s="2">
+        <v>0</v>
+      </c>
+      <c r="I483" s="1">
+        <v>46118.795949074076</v>
+      </c>
+      <c r="J483">
+        <v>1</v>
+      </c>
+      <c r="K483" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="484" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B484" t="s">
+        <v>30</v>
+      </c>
+      <c r="C484">
+        <v>1942</v>
+      </c>
+      <c r="D484" t="s">
+        <v>49</v>
+      </c>
+      <c r="E484" t="s">
+        <v>36</v>
+      </c>
+      <c r="F484" t="s">
+        <v>63</v>
+      </c>
+      <c r="G484" t="s">
+        <v>13</v>
+      </c>
+      <c r="H484" s="2">
+        <v>0</v>
+      </c>
+      <c r="I484" s="1">
+        <v>46118.796643518515</v>
+      </c>
+      <c r="J484">
+        <v>1</v>
+      </c>
+      <c r="K484" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="485" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B485" t="s">
+        <v>30</v>
+      </c>
+      <c r="C485">
+        <v>1944</v>
+      </c>
+      <c r="D485" t="s">
+        <v>51</v>
+      </c>
+      <c r="E485" t="s">
+        <v>36</v>
+      </c>
+      <c r="F485" t="s">
+        <v>63</v>
+      </c>
+      <c r="G485" t="s">
+        <v>10</v>
+      </c>
+      <c r="H485" s="2">
+        <v>0.16244212962962962</v>
+      </c>
+      <c r="I485" s="1">
+        <v>46118.796643518515</v>
+      </c>
+      <c r="J485">
+        <v>1</v>
+      </c>
+      <c r="K485" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="486" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H486" s="2"/>
       <c r="I486" s="1"/>
     </row>
-    <row r="487" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H487" s="2"/>
       <c r="I487" s="1"/>
     </row>
-    <row r="488" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H488" s="2"/>
       <c r="I488" s="1"/>
     </row>
-    <row r="489" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H489" s="2"/>
       <c r="I489" s="1"/>
     </row>
-    <row r="490" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H490" s="2"/>
       <c r="I490" s="1"/>
     </row>
-    <row r="491" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H491" s="2"/>
       <c r="I491" s="1"/>
     </row>
-    <row r="492" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H492" s="2"/>
       <c r="I492" s="1"/>
     </row>
-    <row r="493" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H493" s="2"/>
       <c r="I493" s="1"/>
     </row>
-    <row r="494" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H494" s="2"/>
       <c r="I494" s="1"/>
     </row>
-    <row r="495" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H495" s="2"/>
       <c r="I495" s="1"/>
     </row>
-    <row r="496" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H496" s="2"/>
       <c r="I496" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mericles - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B0F656-1375-41B4-81F8-3DDFA396A39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1012CF0E-26CE-4901-8388-5B9120635A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -14191,7 +14191,7 @@
         <v>46118.811805555553</v>
       </c>
       <c r="J471">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K471" t="s">
         <v>11</v>
@@ -14220,7 +14220,7 @@
         <v>46118.8125</v>
       </c>
       <c r="J472">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K472" t="s">
         <v>11</v>
@@ -14252,7 +14252,7 @@
         <v>46118.813194444447</v>
       </c>
       <c r="J473">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K473" t="s">
         <v>11</v>
@@ -14284,7 +14284,7 @@
         <v>46118.813194444447</v>
       </c>
       <c r="J474">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K474" t="s">
         <v>11</v>
@@ -14313,7 +14313,7 @@
         <v>46118.813888888886</v>
       </c>
       <c r="J475">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K475" t="s">
         <v>11</v>
@@ -14365,16 +14365,16 @@
         <v>63</v>
       </c>
       <c r="G477" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H477" s="2">
-        <v>0</v>
+        <v>7.3611111111111108E-3</v>
       </c>
       <c r="I477" s="1">
         <v>46118.793171296296</v>
       </c>
       <c r="J477">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K477" t="s">
         <v>11</v>
@@ -14406,7 +14406,7 @@
         <v>46118.793865740743</v>
       </c>
       <c r="J478">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K478" t="s">
         <v>11</v>
@@ -14438,7 +14438,7 @@
         <v>46118.794560185182</v>
       </c>
       <c r="J479">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K479" t="s">
         <v>11</v>
@@ -14502,7 +14502,7 @@
         <v>46118.795254629629</v>
       </c>
       <c r="J481">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K481" t="s">
         <v>11</v>
@@ -14534,7 +14534,7 @@
         <v>46118.795254629629</v>
       </c>
       <c r="J482">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K482" t="s">
         <v>11</v>
@@ -14566,7 +14566,7 @@
         <v>46118.795949074076</v>
       </c>
       <c r="J483">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K483" t="s">
         <v>11</v>
@@ -14598,7 +14598,7 @@
         <v>46118.796643518515</v>
       </c>
       <c r="J484">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K484" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mericles - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1012CF0E-26CE-4901-8388-5B9120635A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57EFE89E-39B1-4217-B96A-7E92558452A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14191,7 +14191,7 @@
         <v>46118.811805555553</v>
       </c>
       <c r="J471">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K471" t="s">
         <v>11</v>
@@ -14220,7 +14220,7 @@
         <v>46118.8125</v>
       </c>
       <c r="J472">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K472" t="s">
         <v>11</v>
@@ -14252,7 +14252,7 @@
         <v>46118.813194444447</v>
       </c>
       <c r="J473">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K473" t="s">
         <v>11</v>
@@ -14284,7 +14284,7 @@
         <v>46118.813194444447</v>
       </c>
       <c r="J474">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K474" t="s">
         <v>11</v>
@@ -14313,7 +14313,7 @@
         <v>46118.813888888886</v>
       </c>
       <c r="J475">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K475" t="s">
         <v>11</v>
@@ -14406,7 +14406,7 @@
         <v>46118.793865740743</v>
       </c>
       <c r="J478">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K478" t="s">
         <v>11</v>
@@ -14438,7 +14438,7 @@
         <v>46118.794560185182</v>
       </c>
       <c r="J479">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K479" t="s">
         <v>11</v>
@@ -14502,7 +14502,7 @@
         <v>46118.795254629629</v>
       </c>
       <c r="J481">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K481" t="s">
         <v>11</v>
@@ -14534,7 +14534,7 @@
         <v>46118.795254629629</v>
       </c>
       <c r="J482">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K482" t="s">
         <v>11</v>
@@ -14566,7 +14566,7 @@
         <v>46118.795949074076</v>
       </c>
       <c r="J483">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K483" t="s">
         <v>11</v>
@@ -14598,7 +14598,7 @@
         <v>46118.796643518515</v>
       </c>
       <c r="J484">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K484" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mericles - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57EFE89E-39B1-4217-B96A-7E92558452A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C672B2F8-D215-47F8-B52E-BA2E314F9152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="810" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2573" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2659" uniqueCount="64">
   <si>
     <t>Company Name</t>
   </si>
@@ -604,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K5929"/>
+  <dimension ref="A1:K5929"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -619,39 +619,39 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>30</v>
       </c>
@@ -680,7 +680,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>30</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>30</v>
       </c>
@@ -738,14 +738,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H5" s="2"/>
       <c r="I5" s="1"/>
       <c r="K5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>30</v>
       </c>
@@ -777,14 +777,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
       <c r="I7" s="1"/>
       <c r="K7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>30</v>
       </c>
@@ -816,14 +816,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="K9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>30</v>
       </c>
@@ -855,14 +855,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H11" s="2"/>
       <c r="I11" s="1"/>
       <c r="K11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>30</v>
       </c>
@@ -894,7 +894,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>30</v>
       </c>
@@ -926,7 +926,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>30</v>
       </c>
@@ -958,7 +958,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>30</v>
       </c>
@@ -990,7 +990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>30</v>
       </c>
@@ -14191,7 +14191,7 @@
         <v>46118.811805555553</v>
       </c>
       <c r="J471">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K471" t="s">
         <v>11</v>
@@ -14220,7 +14220,7 @@
         <v>46118.8125</v>
       </c>
       <c r="J472">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K472" t="s">
         <v>11</v>
@@ -14252,7 +14252,7 @@
         <v>46118.813194444447</v>
       </c>
       <c r="J473">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K473" t="s">
         <v>11</v>
@@ -14284,7 +14284,7 @@
         <v>46118.813194444447</v>
       </c>
       <c r="J474">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K474" t="s">
         <v>11</v>
@@ -14313,7 +14313,7 @@
         <v>46118.813888888886</v>
       </c>
       <c r="J475">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K475" t="s">
         <v>11</v>
@@ -14406,7 +14406,7 @@
         <v>46118.793865740743</v>
       </c>
       <c r="J478">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K478" t="s">
         <v>11</v>
@@ -14438,7 +14438,7 @@
         <v>46118.794560185182</v>
       </c>
       <c r="J479">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K479" t="s">
         <v>11</v>
@@ -14502,7 +14502,7 @@
         <v>46118.795254629629</v>
       </c>
       <c r="J481">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K481" t="s">
         <v>11</v>
@@ -14534,7 +14534,7 @@
         <v>46118.795254629629</v>
       </c>
       <c r="J482">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K482" t="s">
         <v>11</v>
@@ -14566,7 +14566,7 @@
         <v>46118.795949074076</v>
       </c>
       <c r="J483">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K483" t="s">
         <v>11</v>
@@ -14598,7 +14598,7 @@
         <v>46118.796643518515</v>
       </c>
       <c r="J484">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K484" t="s">
         <v>11</v>
@@ -14637,110 +14637,518 @@
       </c>
     </row>
     <row r="486" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H486" s="2"/>
-      <c r="I486" s="1"/>
+      <c r="B486" t="s">
+        <v>30</v>
+      </c>
+      <c r="C486">
+        <v>1926</v>
+      </c>
+      <c r="D486" t="s">
+        <v>31</v>
+      </c>
+      <c r="F486" t="s">
+        <v>18</v>
+      </c>
+      <c r="G486" t="s">
+        <v>13</v>
+      </c>
+      <c r="H486" s="2">
+        <v>0</v>
+      </c>
+      <c r="I486" s="1">
+        <v>46146.680902777778</v>
+      </c>
+      <c r="J486">
+        <v>0</v>
+      </c>
+      <c r="K486" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="487" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H487" s="2"/>
-      <c r="I487" s="1"/>
+      <c r="B487" t="s">
+        <v>30</v>
+      </c>
+      <c r="C487">
+        <v>1927</v>
+      </c>
+      <c r="D487" t="s">
+        <v>33</v>
+      </c>
+      <c r="F487" t="s">
+        <v>18</v>
+      </c>
+      <c r="G487" t="s">
+        <v>13</v>
+      </c>
+      <c r="H487" s="2">
+        <v>0</v>
+      </c>
+      <c r="I487" s="1">
+        <v>46146.680902777778</v>
+      </c>
+      <c r="J487">
+        <v>0</v>
+      </c>
+      <c r="K487" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="488" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H488" s="2"/>
-      <c r="I488" s="1"/>
+      <c r="B488" t="s">
+        <v>30</v>
+      </c>
+      <c r="C488">
+        <v>3789</v>
+      </c>
+      <c r="D488" t="s">
+        <v>60</v>
+      </c>
+      <c r="E488" t="s">
+        <v>36</v>
+      </c>
+      <c r="F488" t="s">
+        <v>18</v>
+      </c>
+      <c r="G488" t="s">
+        <v>13</v>
+      </c>
+      <c r="H488" s="2">
+        <v>0</v>
+      </c>
+      <c r="I488" s="1">
+        <v>46146.681597222225</v>
+      </c>
+      <c r="J488">
+        <v>0</v>
+      </c>
+      <c r="K488" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="489" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H489" s="2"/>
-      <c r="I489" s="1"/>
+      <c r="B489" t="s">
+        <v>30</v>
+      </c>
+      <c r="C489">
+        <v>1932</v>
+      </c>
+      <c r="D489" t="s">
+        <v>39</v>
+      </c>
+      <c r="E489" t="s">
+        <v>36</v>
+      </c>
+      <c r="F489" t="s">
+        <v>18</v>
+      </c>
+      <c r="G489" t="s">
+        <v>13</v>
+      </c>
+      <c r="H489" s="2">
+        <v>0</v>
+      </c>
+      <c r="I489" s="1">
+        <v>46146.681597222225</v>
+      </c>
+      <c r="J489">
+        <v>0</v>
+      </c>
+      <c r="K489" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="490" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H490" s="2"/>
-      <c r="I490" s="1"/>
+      <c r="B490" t="s">
+        <v>30</v>
+      </c>
+      <c r="C490">
+        <v>2977</v>
+      </c>
+      <c r="D490" t="s">
+        <v>56</v>
+      </c>
+      <c r="F490" t="s">
+        <v>18</v>
+      </c>
+      <c r="G490" t="s">
+        <v>13</v>
+      </c>
+      <c r="H490" s="2">
+        <v>0</v>
+      </c>
+      <c r="I490" s="1">
+        <v>46146.682291666664</v>
+      </c>
+      <c r="J490">
+        <v>0</v>
+      </c>
+      <c r="K490" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="491" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H491" s="2"/>
-      <c r="I491" s="1"/>
+      <c r="B491" t="s">
+        <v>30</v>
+      </c>
+      <c r="C491">
+        <v>1935</v>
+      </c>
+      <c r="D491" t="s">
+        <v>42</v>
+      </c>
+      <c r="E491" t="s">
+        <v>36</v>
+      </c>
+      <c r="F491" t="s">
+        <v>18</v>
+      </c>
+      <c r="G491" t="s">
+        <v>13</v>
+      </c>
+      <c r="H491" s="2">
+        <v>0</v>
+      </c>
+      <c r="I491" s="1">
+        <v>46146.682986111111</v>
+      </c>
+      <c r="J491">
+        <v>0</v>
+      </c>
+      <c r="K491" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="492" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H492" s="2"/>
-      <c r="I492" s="1"/>
+      <c r="B492" t="s">
+        <v>30</v>
+      </c>
+      <c r="C492">
+        <v>1936</v>
+      </c>
+      <c r="D492" t="s">
+        <v>43</v>
+      </c>
+      <c r="F492" t="s">
+        <v>18</v>
+      </c>
+      <c r="G492" t="s">
+        <v>13</v>
+      </c>
+      <c r="H492" s="2">
+        <v>0</v>
+      </c>
+      <c r="I492" s="1">
+        <v>46146.682986111111</v>
+      </c>
+      <c r="J492">
+        <v>0</v>
+      </c>
+      <c r="K492" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="493" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H493" s="2"/>
-      <c r="I493" s="1"/>
+      <c r="B493" t="s">
+        <v>30</v>
+      </c>
+      <c r="C493">
+        <v>3890</v>
+      </c>
+      <c r="D493" t="s">
+        <v>62</v>
+      </c>
+      <c r="E493" t="s">
+        <v>36</v>
+      </c>
+      <c r="F493" t="s">
+        <v>18</v>
+      </c>
+      <c r="G493" t="s">
+        <v>13</v>
+      </c>
+      <c r="H493" s="2">
+        <v>0</v>
+      </c>
+      <c r="I493" s="1">
+        <v>46146.683680555558</v>
+      </c>
+      <c r="J493">
+        <v>0</v>
+      </c>
+      <c r="K493" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="494" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H494" s="2"/>
-      <c r="I494" s="1"/>
+      <c r="B494" t="s">
+        <v>30</v>
+      </c>
+      <c r="C494">
+        <v>1937</v>
+      </c>
+      <c r="D494" t="s">
+        <v>44</v>
+      </c>
+      <c r="E494" t="s">
+        <v>36</v>
+      </c>
+      <c r="F494" t="s">
+        <v>18</v>
+      </c>
+      <c r="G494" t="s">
+        <v>13</v>
+      </c>
+      <c r="H494" s="2">
+        <v>0</v>
+      </c>
+      <c r="I494" s="1">
+        <v>46146.684374999997</v>
+      </c>
+      <c r="J494">
+        <v>0</v>
+      </c>
+      <c r="K494" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="495" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H495" s="2"/>
-      <c r="I495" s="1"/>
+      <c r="B495" t="s">
+        <v>30</v>
+      </c>
+      <c r="C495">
+        <v>3788</v>
+      </c>
+      <c r="D495" t="s">
+        <v>61</v>
+      </c>
+      <c r="E495" t="s">
+        <v>36</v>
+      </c>
+      <c r="F495" t="s">
+        <v>18</v>
+      </c>
+      <c r="G495" t="s">
+        <v>13</v>
+      </c>
+      <c r="H495" s="2">
+        <v>0</v>
+      </c>
+      <c r="I495" s="1">
+        <v>46146.684374999997</v>
+      </c>
+      <c r="J495">
+        <v>0</v>
+      </c>
+      <c r="K495" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="496" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H496" s="2"/>
-      <c r="I496" s="1"/>
-    </row>
-    <row r="497" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H497" s="2"/>
-      <c r="I497" s="1"/>
-    </row>
-    <row r="498" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H498" s="2"/>
-      <c r="I498" s="1"/>
-    </row>
-    <row r="499" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H499" s="2"/>
-      <c r="I499" s="1"/>
-    </row>
-    <row r="500" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H500" s="2"/>
-      <c r="I500" s="1"/>
-    </row>
-    <row r="501" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B496" t="s">
+        <v>30</v>
+      </c>
+      <c r="C496">
+        <v>3868</v>
+      </c>
+      <c r="D496" t="s">
+        <v>36</v>
+      </c>
+      <c r="E496" t="s">
+        <v>36</v>
+      </c>
+      <c r="F496" t="s">
+        <v>18</v>
+      </c>
+      <c r="G496" t="s">
+        <v>13</v>
+      </c>
+      <c r="H496" s="2">
+        <v>0</v>
+      </c>
+      <c r="I496" s="1">
+        <v>46146.685069444444</v>
+      </c>
+      <c r="J496">
+        <v>0</v>
+      </c>
+      <c r="K496" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="497" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B497" t="s">
+        <v>30</v>
+      </c>
+      <c r="C497">
+        <v>1939</v>
+      </c>
+      <c r="D497" t="s">
+        <v>46</v>
+      </c>
+      <c r="E497" t="s">
+        <v>36</v>
+      </c>
+      <c r="F497" t="s">
+        <v>18</v>
+      </c>
+      <c r="G497" t="s">
+        <v>13</v>
+      </c>
+      <c r="H497" s="2">
+        <v>0</v>
+      </c>
+      <c r="I497" s="1">
+        <v>46146.685763888891</v>
+      </c>
+      <c r="J497">
+        <v>0</v>
+      </c>
+      <c r="K497" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="498" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B498" t="s">
+        <v>30</v>
+      </c>
+      <c r="C498">
+        <v>1941</v>
+      </c>
+      <c r="D498" t="s">
+        <v>48</v>
+      </c>
+      <c r="E498" t="s">
+        <v>36</v>
+      </c>
+      <c r="F498" t="s">
+        <v>18</v>
+      </c>
+      <c r="G498" t="s">
+        <v>13</v>
+      </c>
+      <c r="H498" s="2">
+        <v>0</v>
+      </c>
+      <c r="I498" s="1">
+        <v>46146.685763888891</v>
+      </c>
+      <c r="J498">
+        <v>0</v>
+      </c>
+      <c r="K498" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="499" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B499" t="s">
+        <v>30</v>
+      </c>
+      <c r="C499">
+        <v>1942</v>
+      </c>
+      <c r="D499" t="s">
+        <v>49</v>
+      </c>
+      <c r="E499" t="s">
+        <v>36</v>
+      </c>
+      <c r="F499" t="s">
+        <v>18</v>
+      </c>
+      <c r="G499" t="s">
+        <v>13</v>
+      </c>
+      <c r="H499" s="2">
+        <v>0</v>
+      </c>
+      <c r="I499" s="1">
+        <v>46146.68645833333</v>
+      </c>
+      <c r="J499">
+        <v>0</v>
+      </c>
+      <c r="K499" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="500" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B500" t="s">
+        <v>30</v>
+      </c>
+      <c r="C500">
+        <v>1944</v>
+      </c>
+      <c r="D500" t="s">
+        <v>51</v>
+      </c>
+      <c r="E500" t="s">
+        <v>36</v>
+      </c>
+      <c r="F500" t="s">
+        <v>18</v>
+      </c>
+      <c r="G500" t="s">
+        <v>13</v>
+      </c>
+      <c r="H500" s="2">
+        <v>0</v>
+      </c>
+      <c r="I500" s="1">
+        <v>46146.687152777777</v>
+      </c>
+      <c r="J500">
+        <v>0</v>
+      </c>
+      <c r="K500" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="501" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H501" s="2"/>
       <c r="I501" s="1"/>
     </row>
-    <row r="502" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H502" s="2"/>
       <c r="I502" s="1"/>
     </row>
-    <row r="503" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H503" s="2"/>
       <c r="I503" s="1"/>
     </row>
-    <row r="504" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H504" s="2"/>
       <c r="I504" s="1"/>
     </row>
-    <row r="505" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H505" s="2"/>
       <c r="I505" s="1"/>
     </row>
-    <row r="506" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H506" s="2"/>
       <c r="I506" s="1"/>
     </row>
-    <row r="507" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H507" s="2"/>
       <c r="I507" s="1"/>
     </row>
-    <row r="508" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H508" s="2"/>
       <c r="I508" s="1"/>
     </row>
-    <row r="509" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H509" s="2"/>
       <c r="I509" s="1"/>
     </row>
-    <row r="510" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H510" s="2"/>
       <c r="I510" s="1"/>
     </row>
-    <row r="511" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H511" s="2"/>
       <c r="I511" s="1"/>
     </row>
-    <row r="512" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H512" s="2"/>
       <c r="I512" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mericles - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C672B2F8-D215-47F8-B52E-BA2E314F9152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B50B631-1EF7-428D-BE81-B5E0EBC018BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -604,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K5929"/>
+  <dimension ref="B1:K5929"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -619,39 +619,39 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>30</v>
       </c>
@@ -680,7 +680,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>30</v>
       </c>
@@ -709,7 +709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>30</v>
       </c>
@@ -738,14 +738,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H5" s="2"/>
       <c r="I5" s="1"/>
       <c r="K5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>30</v>
       </c>
@@ -777,14 +777,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H7" s="2"/>
       <c r="I7" s="1"/>
       <c r="K7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>30</v>
       </c>
@@ -816,14 +816,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="K9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>30</v>
       </c>
@@ -855,14 +855,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H11" s="2"/>
       <c r="I11" s="1"/>
       <c r="K11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>30</v>
       </c>
@@ -894,7 +894,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>30</v>
       </c>
@@ -926,7 +926,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>30</v>
       </c>
@@ -958,7 +958,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>30</v>
       </c>
@@ -990,7 +990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>30</v>
       </c>
@@ -14191,7 +14191,7 @@
         <v>46118.811805555553</v>
       </c>
       <c r="J471">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K471" t="s">
         <v>11</v>
@@ -14220,7 +14220,7 @@
         <v>46118.8125</v>
       </c>
       <c r="J472">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K472" t="s">
         <v>11</v>
@@ -14252,7 +14252,7 @@
         <v>46118.813194444447</v>
       </c>
       <c r="J473">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K473" t="s">
         <v>11</v>
@@ -14284,7 +14284,7 @@
         <v>46118.813194444447</v>
       </c>
       <c r="J474">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K474" t="s">
         <v>11</v>
@@ -14313,7 +14313,7 @@
         <v>46118.813888888886</v>
       </c>
       <c r="J475">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K475" t="s">
         <v>11</v>
@@ -14406,7 +14406,7 @@
         <v>46118.793865740743</v>
       </c>
       <c r="J478">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K478" t="s">
         <v>11</v>
@@ -14438,7 +14438,7 @@
         <v>46118.794560185182</v>
       </c>
       <c r="J479">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K479" t="s">
         <v>11</v>
@@ -14502,7 +14502,7 @@
         <v>46118.795254629629</v>
       </c>
       <c r="J481">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K481" t="s">
         <v>11</v>
@@ -14534,7 +14534,7 @@
         <v>46118.795254629629</v>
       </c>
       <c r="J482">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K482" t="s">
         <v>11</v>
@@ -14566,7 +14566,7 @@
         <v>46118.795949074076</v>
       </c>
       <c r="J483">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K483" t="s">
         <v>11</v>
@@ -14598,7 +14598,7 @@
         <v>46118.796643518515</v>
       </c>
       <c r="J484">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K484" t="s">
         <v>11</v>
@@ -14804,10 +14804,10 @@
         <v>18</v>
       </c>
       <c r="G491" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H491" s="2">
-        <v>0</v>
+        <v>5.8333333333333336E-3</v>
       </c>
       <c r="I491" s="1">
         <v>46146.682986111111</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Mericles - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D485BB8-AF67-4D92-8574-875BAB7636D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D24A50D-48A8-477E-BB43-26DFA60AF4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -14666,7 +14666,7 @@
         <v>46146.680902777778</v>
       </c>
       <c r="J487">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K487" t="s">
         <v>11</v>
@@ -14695,7 +14695,7 @@
         <v>46146.680902777778</v>
       </c>
       <c r="J488">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K488" t="s">
         <v>11</v>
@@ -14727,7 +14727,7 @@
         <v>46146.681597222225</v>
       </c>
       <c r="J489">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K489" t="s">
         <v>11</v>
@@ -14759,7 +14759,7 @@
         <v>46146.681597222225</v>
       </c>
       <c r="J490">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K490" t="s">
         <v>11</v>
@@ -14788,7 +14788,7 @@
         <v>46146.682291666664</v>
       </c>
       <c r="J491">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K491" t="s">
         <v>11</v>
@@ -14888,7 +14888,7 @@
         <v>46146.683680555558</v>
       </c>
       <c r="J495">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K495" t="s">
         <v>11</v>
@@ -14920,7 +14920,7 @@
         <v>46146.684374999997</v>
       </c>
       <c r="J496">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K496" t="s">
         <v>11</v>
@@ -14984,7 +14984,7 @@
         <v>46146.685069444444</v>
       </c>
       <c r="J498">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K498" t="s">
         <v>11</v>
@@ -15016,7 +15016,7 @@
         <v>46146.685763888891</v>
       </c>
       <c r="J499">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K499" t="s">
         <v>11</v>
@@ -15048,7 +15048,7 @@
         <v>46146.685763888891</v>
       </c>
       <c r="J500">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K500" t="s">
         <v>11</v>
@@ -15080,7 +15080,7 @@
         <v>46146.68645833333</v>
       </c>
       <c r="J501">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K501" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Mericles - Samsara\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\mericles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD17D7A8-E5C9-470E-B759-B5F9D006CEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067BB341-22BA-4FC9-84DD-8301737AA3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15476,7 +15476,7 @@
         <v>46176.466782407406</v>
       </c>
       <c r="J511">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K511" t="s">
         <v>11</v>
@@ -15505,7 +15505,7 @@
         <v>46176.466782407406</v>
       </c>
       <c r="J512">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K512" t="s">
         <v>11</v>
@@ -15537,7 +15537,7 @@
         <v>46176.467476851853</v>
       </c>
       <c r="J513">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K513" t="s">
         <v>11</v>
@@ -15598,7 +15598,7 @@
         <v>46176.467476851853</v>
       </c>
       <c r="J515">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K515" t="s">
         <v>11</v>
@@ -15758,7 +15758,7 @@
         <v>46176.468865740739</v>
       </c>
       <c r="J520">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K520" t="s">
         <v>11</v>
@@ -15781,16 +15781,16 @@
         <v>35</v>
       </c>
       <c r="G521" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H521" s="2">
-        <v>0</v>
+        <v>0.16229166666666667</v>
       </c>
       <c r="I521" s="1">
         <v>46187.710300925923</v>
       </c>
       <c r="J521">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K521" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\mericles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15D0C532-5C0C-40C4-AEBD-6AC53B622A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C0F6BD5-F9A5-4F0D-9414-0048F77E05E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -89,6 +89,9 @@
     <t>Speed Management</t>
   </si>
   <si>
+    <t>Vehicle Inspections</t>
+  </si>
+  <si>
     <t>Winter Weather</t>
   </si>
   <si>
@@ -101,13 +104,22 @@
     <t>Space Management-Big 5</t>
   </si>
   <si>
+    <t>Distracted Driving</t>
+  </si>
+  <si>
     <t>Alert Driving</t>
+  </si>
+  <si>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
@@ -119,34 +131,22 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Vehicle Inspections</t>
+    <t>Work Zone Safety</t>
   </si>
   <si>
-    <t>Distracted Driving</t>
-  </si>
-  <si>
-    <t>In Cab Distractions</t>
-  </si>
-  <si>
-    <t>Driver Health</t>
-  </si>
-  <si>
-    <t>Work Zone Safety</t>
+    <t>Scene of an Accident</t>
   </si>
   <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
   </si>
   <si>
-    <t>Fire Extinguisher Training for CDL</t>
-  </si>
-  <si>
     <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
-    <t>Scene of an Accident</t>
+    <t>DOT Reasonable Suspicion: The Power of the Three R’s</t>
   </si>
   <si>
-    <t>DOT Reasonable Suspicion: The Power of the Three R’s</t>
+    <t>In Cab Distractions</t>
   </si>
   <si>
     <t>Mericle's Towing</t>
@@ -610,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -750,7 +750,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="1"/>
       <c r="M5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
@@ -791,7 +791,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="1"/>
       <c r="M7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
@@ -832,7 +832,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="1"/>
       <c r="M9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
@@ -873,7 +873,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="1"/>
       <c r="M11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
@@ -1135,7 +1135,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="1"/>
       <c r="M20" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
@@ -1208,7 +1208,7 @@
       <c r="J23" s="2"/>
       <c r="K23" s="1"/>
       <c r="M23" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
@@ -1281,7 +1281,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="1"/>
       <c r="M26" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
@@ -1441,7 +1441,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="1"/>
       <c r="M32" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
@@ -1514,7 +1514,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="1"/>
       <c r="M35" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
@@ -1651,7 +1651,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="1"/>
       <c r="M40" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
@@ -1721,7 +1721,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="1"/>
       <c r="M43" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
@@ -1794,7 +1794,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="1"/>
       <c r="M46" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
@@ -1995,7 +1995,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="1"/>
       <c r="M53" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
@@ -2065,7 +2065,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="1"/>
       <c r="M56" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
@@ -2196,7 +2196,7 @@
       <c r="J61" s="2"/>
       <c r="K61" s="1"/>
       <c r="M61" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
@@ -2237,7 +2237,7 @@
       <c r="J63" s="2"/>
       <c r="K63" s="1"/>
       <c r="M63" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
@@ -2278,7 +2278,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="1"/>
       <c r="M65" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
@@ -2476,7 +2476,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="1"/>
       <c r="M72" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
@@ -2549,7 +2549,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="1"/>
       <c r="M75" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
@@ -2622,7 +2622,7 @@
       <c r="J78" s="2"/>
       <c r="K78" s="1"/>
       <c r="M78" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
@@ -2695,7 +2695,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="1"/>
       <c r="M81" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
@@ -2741,7 +2741,7 @@
         <v>37</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>12</v>
@@ -2765,7 +2765,7 @@
       <c r="J84" s="2"/>
       <c r="K84" s="1"/>
       <c r="M84" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
@@ -2782,7 +2782,7 @@
         <v>42</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>13</v>
@@ -2814,7 +2814,7 @@
         <v>42</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>12</v>
@@ -2838,7 +2838,7 @@
       <c r="J87" s="2"/>
       <c r="K87" s="1"/>
       <c r="M87" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
@@ -2855,7 +2855,7 @@
         <v>42</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -2887,7 +2887,7 @@
         <v>42</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -2919,7 +2919,7 @@
         <v>42</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>13</v>
@@ -2948,7 +2948,7 @@
         <v>49</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>13</v>
@@ -2980,7 +2980,7 @@
         <v>42</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>13</v>
@@ -3012,7 +3012,7 @@
         <v>42</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>13</v>
@@ -3044,7 +3044,7 @@
         <v>42</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>13</v>
@@ -3076,7 +3076,7 @@
         <v>42</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>13</v>
@@ -3108,7 +3108,7 @@
         <v>42</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>13</v>
@@ -3140,7 +3140,7 @@
         <v>42</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>13</v>
@@ -3172,7 +3172,7 @@
         <v>42</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>12</v>
@@ -3196,7 +3196,7 @@
       <c r="J99" s="2"/>
       <c r="K99" s="1"/>
       <c r="M99" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
@@ -3213,7 +3213,7 @@
         <v>42</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>14</v>
@@ -3237,7 +3237,7 @@
       <c r="J101" s="2"/>
       <c r="K101" s="1"/>
       <c r="M101" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.3">
@@ -3589,7 +3589,7 @@
       <c r="J113" s="2"/>
       <c r="K113" s="1"/>
       <c r="M113" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
@@ -3691,7 +3691,7 @@
       <c r="J117" s="2"/>
       <c r="K117" s="1"/>
       <c r="M117" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="118" spans="4:13" x14ac:dyDescent="0.3">
@@ -3897,7 +3897,7 @@
         <v>37</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>13</v>
@@ -3926,7 +3926,7 @@
         <v>39</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>13</v>
@@ -3955,7 +3955,7 @@
         <v>40</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -3987,7 +3987,7 @@
         <v>42</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>14</v>
@@ -4011,7 +4011,7 @@
       <c r="J128" s="2"/>
       <c r="K128" s="1"/>
       <c r="M128" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
@@ -4028,7 +4028,7 @@
         <v>42</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>10</v>
@@ -4060,7 +4060,7 @@
         <v>42</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4092,7 +4092,7 @@
         <v>42</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>13</v>
@@ -4124,7 +4124,7 @@
         <v>42</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>13</v>
@@ -4156,7 +4156,7 @@
         <v>42</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>13</v>
@@ -4188,7 +4188,7 @@
         <v>42</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4220,7 +4220,7 @@
         <v>42</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>13</v>
@@ -4249,7 +4249,7 @@
         <v>49</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>13</v>
@@ -4281,7 +4281,7 @@
         <v>42</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>13</v>
@@ -4313,7 +4313,7 @@
         <v>42</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>13</v>
@@ -4345,7 +4345,7 @@
         <v>42</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>13</v>
@@ -4377,7 +4377,7 @@
         <v>42</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>14</v>
@@ -4401,7 +4401,7 @@
       <c r="J141" s="2"/>
       <c r="K141" s="1"/>
       <c r="M141" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="142" spans="4:13" x14ac:dyDescent="0.3">
@@ -4418,7 +4418,7 @@
         <v>42</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>13</v>
@@ -4450,7 +4450,7 @@
         <v>42</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>13</v>
@@ -4482,7 +4482,7 @@
         <v>42</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>13</v>
@@ -4514,7 +4514,7 @@
         <v>42</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>13</v>
@@ -4543,7 +4543,7 @@
         <v>37</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>13</v>
@@ -4572,7 +4572,7 @@
         <v>39</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>13</v>
@@ -4601,7 +4601,7 @@
         <v>40</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>13</v>
@@ -4633,7 +4633,7 @@
         <v>42</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>13</v>
@@ -4665,7 +4665,7 @@
         <v>42</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>13</v>
@@ -4697,7 +4697,7 @@
         <v>42</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>13</v>
@@ -4729,7 +4729,7 @@
         <v>42</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>13</v>
@@ -4761,7 +4761,7 @@
         <v>42</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>13</v>
@@ -4793,7 +4793,7 @@
         <v>42</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>13</v>
@@ -4825,7 +4825,7 @@
         <v>42</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>10</v>
@@ -4857,7 +4857,7 @@
         <v>42</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>13</v>
@@ -4886,7 +4886,7 @@
         <v>49</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>13</v>
@@ -4918,7 +4918,7 @@
         <v>42</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>13</v>
@@ -4950,7 +4950,7 @@
         <v>42</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>13</v>
@@ -4982,7 +4982,7 @@
         <v>42</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>13</v>
@@ -5014,7 +5014,7 @@
         <v>42</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>12</v>
@@ -5038,7 +5038,7 @@
       <c r="J162" s="2"/>
       <c r="K162" s="1"/>
       <c r="M162" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="163" spans="4:13" x14ac:dyDescent="0.3">
@@ -5055,7 +5055,7 @@
         <v>42</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>10</v>
@@ -5087,7 +5087,7 @@
         <v>42</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>13</v>
@@ -5119,7 +5119,7 @@
         <v>42</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>13</v>
@@ -5151,7 +5151,7 @@
         <v>42</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>13</v>
@@ -5180,7 +5180,7 @@
         <v>37</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>13</v>
@@ -5209,7 +5209,7 @@
         <v>39</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>10</v>
@@ -5238,7 +5238,7 @@
         <v>40</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>13</v>
@@ -5270,7 +5270,7 @@
         <v>42</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>10</v>
@@ -5302,7 +5302,7 @@
         <v>42</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>10</v>
@@ -5334,7 +5334,7 @@
         <v>42</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>10</v>
@@ -5366,7 +5366,7 @@
         <v>42</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>10</v>
@@ -5398,7 +5398,7 @@
         <v>42</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>10</v>
@@ -5430,7 +5430,7 @@
         <v>42</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>13</v>
@@ -5462,7 +5462,7 @@
         <v>42</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>10</v>
@@ -5494,7 +5494,7 @@
         <v>42</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>10</v>
@@ -5523,7 +5523,7 @@
         <v>49</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>10</v>
@@ -5555,7 +5555,7 @@
         <v>42</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>10</v>
@@ -5587,7 +5587,7 @@
         <v>42</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>12</v>
@@ -5611,7 +5611,7 @@
       <c r="J181" s="2"/>
       <c r="K181" s="1"/>
       <c r="M181" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="182" spans="4:13" x14ac:dyDescent="0.3">
@@ -5628,7 +5628,7 @@
         <v>42</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>13</v>
@@ -5660,7 +5660,7 @@
         <v>42</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>10</v>
@@ -5692,7 +5692,7 @@
         <v>42</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>10</v>
@@ -5724,7 +5724,7 @@
         <v>42</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>13</v>
@@ -5756,7 +5756,7 @@
         <v>42</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>13</v>
@@ -5788,7 +5788,7 @@
         <v>42</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>10</v>
@@ -5817,7 +5817,7 @@
         <v>37</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>13</v>
@@ -5846,7 +5846,7 @@
         <v>39</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>10</v>
@@ -5875,7 +5875,7 @@
         <v>40</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>13</v>
@@ -5907,7 +5907,7 @@
         <v>42</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>10</v>
@@ -5939,7 +5939,7 @@
         <v>42</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>13</v>
@@ -5971,7 +5971,7 @@
         <v>42</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>13</v>
@@ -6003,7 +6003,7 @@
         <v>42</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>10</v>
@@ -6032,7 +6032,7 @@
         <v>61</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>10</v>
@@ -6064,7 +6064,7 @@
         <v>42</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>13</v>
@@ -6093,7 +6093,7 @@
         <v>62</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>14</v>
@@ -6117,7 +6117,7 @@
       <c r="J198" s="2"/>
       <c r="K198" s="1"/>
       <c r="M198" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="199" spans="4:13" x14ac:dyDescent="0.3">
@@ -6134,7 +6134,7 @@
         <v>42</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>10</v>
@@ -6166,7 +6166,7 @@
         <v>42</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>10</v>
@@ -6195,7 +6195,7 @@
         <v>49</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>10</v>
@@ -6227,7 +6227,7 @@
         <v>42</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>10</v>
@@ -6259,7 +6259,7 @@
         <v>42</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>10</v>
@@ -6291,7 +6291,7 @@
         <v>42</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>13</v>
@@ -6323,7 +6323,7 @@
         <v>42</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>12</v>
@@ -6347,7 +6347,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
       <c r="M206" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="207" spans="4:13" x14ac:dyDescent="0.3">
@@ -6364,7 +6364,7 @@
         <v>42</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>13</v>
@@ -6396,7 +6396,7 @@
         <v>42</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>13</v>
@@ -6428,7 +6428,7 @@
         <v>42</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>13</v>
@@ -6460,7 +6460,7 @@
         <v>42</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>10</v>
@@ -6492,7 +6492,7 @@
         <v>42</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>13</v>
@@ -6521,7 +6521,7 @@
         <v>37</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>13</v>
@@ -6550,7 +6550,7 @@
         <v>39</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>10</v>
@@ -6582,7 +6582,7 @@
         <v>42</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>10</v>
@@ -6614,7 +6614,7 @@
         <v>42</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>13</v>
@@ -6646,7 +6646,7 @@
         <v>42</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>10</v>
@@ -6678,7 +6678,7 @@
         <v>42</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>10</v>
@@ -6707,7 +6707,7 @@
         <v>61</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>13</v>
@@ -6739,7 +6739,7 @@
         <v>42</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>13</v>
@@ -6768,7 +6768,7 @@
         <v>62</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>12</v>
@@ -6792,7 +6792,7 @@
       <c r="J221" s="2"/>
       <c r="K221" s="1"/>
       <c r="M221" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="222" spans="4:13" x14ac:dyDescent="0.3">
@@ -6809,7 +6809,7 @@
         <v>42</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>10</v>
@@ -6841,7 +6841,7 @@
         <v>42</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>13</v>
@@ -6870,7 +6870,7 @@
         <v>49</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>13</v>
@@ -6902,7 +6902,7 @@
         <v>42</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>12</v>
@@ -6926,7 +6926,7 @@
       <c r="J226" s="2"/>
       <c r="K226" s="1"/>
       <c r="M226" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="227" spans="4:13" x14ac:dyDescent="0.3">
@@ -6943,7 +6943,7 @@
         <v>42</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>13</v>
@@ -6975,7 +6975,7 @@
         <v>42</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>13</v>
@@ -7007,7 +7007,7 @@
         <v>42</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>10</v>
@@ -7039,7 +7039,7 @@
         <v>42</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>10</v>
@@ -7071,7 +7071,7 @@
         <v>42</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>13</v>
@@ -7103,7 +7103,7 @@
         <v>42</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>13</v>
@@ -7135,7 +7135,7 @@
         <v>42</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>13</v>
@@ -7164,7 +7164,7 @@
         <v>37</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>13</v>
@@ -7193,7 +7193,7 @@
         <v>39</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>12</v>
@@ -7217,7 +7217,7 @@
       <c r="J236" s="2"/>
       <c r="K236" s="1"/>
       <c r="M236" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="237" spans="4:13" x14ac:dyDescent="0.3">
@@ -7234,7 +7234,7 @@
         <v>42</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>13</v>
@@ -7266,7 +7266,7 @@
         <v>42</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>13</v>
@@ -7298,7 +7298,7 @@
         <v>42</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>13</v>
@@ -7330,7 +7330,7 @@
         <v>42</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>13</v>
@@ -7359,7 +7359,7 @@
         <v>61</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>12</v>
@@ -7383,7 +7383,7 @@
       <c r="J242" s="2"/>
       <c r="K242" s="1"/>
       <c r="M242" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="243" spans="4:13" x14ac:dyDescent="0.3">
@@ -7400,7 +7400,7 @@
         <v>42</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>13</v>
@@ -7429,7 +7429,7 @@
         <v>62</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>12</v>
@@ -7453,7 +7453,7 @@
       <c r="J245" s="2"/>
       <c r="K245" s="1"/>
       <c r="M245" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="246" spans="4:13" x14ac:dyDescent="0.3">
@@ -7470,7 +7470,7 @@
         <v>42</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>10</v>
@@ -7502,7 +7502,7 @@
         <v>42</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>10</v>
@@ -7531,7 +7531,7 @@
         <v>49</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>10</v>
@@ -7563,7 +7563,7 @@
         <v>42</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>10</v>
@@ -7595,7 +7595,7 @@
         <v>42</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>13</v>
@@ -7627,7 +7627,7 @@
         <v>42</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>13</v>
@@ -7659,7 +7659,7 @@
         <v>42</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7691,7 +7691,7 @@
         <v>42</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>13</v>
@@ -7723,7 +7723,7 @@
         <v>42</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>13</v>
@@ -7755,7 +7755,7 @@
         <v>42</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>10</v>
@@ -7784,7 +7784,7 @@
         <v>37</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>13</v>
@@ -7813,7 +7813,7 @@
         <v>39</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>10</v>
@@ -7845,7 +7845,7 @@
         <v>42</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>13</v>
@@ -7877,7 +7877,7 @@
         <v>42</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>13</v>
@@ -7909,7 +7909,7 @@
         <v>42</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>13</v>
@@ -7941,7 +7941,7 @@
         <v>42</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>10</v>
@@ -7970,7 +7970,7 @@
         <v>61</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>13</v>
@@ -8002,7 +8002,7 @@
         <v>42</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>13</v>
@@ -8031,7 +8031,7 @@
         <v>62</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>13</v>
@@ -8063,7 +8063,7 @@
         <v>42</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>10</v>
@@ -8095,7 +8095,7 @@
         <v>42</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>10</v>
@@ -8124,7 +8124,7 @@
         <v>49</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>10</v>
@@ -8156,7 +8156,7 @@
         <v>42</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>10</v>
@@ -8188,7 +8188,7 @@
         <v>42</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>13</v>
@@ -8220,7 +8220,7 @@
         <v>42</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>13</v>
@@ -8252,7 +8252,7 @@
         <v>42</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>13</v>
@@ -8284,7 +8284,7 @@
         <v>42</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>13</v>
@@ -8316,7 +8316,7 @@
         <v>42</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>13</v>
@@ -8348,7 +8348,7 @@
         <v>42</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>13</v>
@@ -8377,7 +8377,7 @@
         <v>37</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>12</v>
@@ -8401,7 +8401,7 @@
       <c r="J276" s="2"/>
       <c r="K276" s="1"/>
       <c r="M276" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="277" spans="4:13" x14ac:dyDescent="0.3">
@@ -8415,7 +8415,7 @@
         <v>39</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>13</v>
@@ -8447,7 +8447,7 @@
         <v>42</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>13</v>
@@ -8479,7 +8479,7 @@
         <v>42</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>13</v>
@@ -8511,7 +8511,7 @@
         <v>42</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>13</v>
@@ -8543,7 +8543,7 @@
         <v>42</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>10</v>
@@ -8572,7 +8572,7 @@
         <v>61</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>13</v>
@@ -8604,7 +8604,7 @@
         <v>42</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>13</v>
@@ -8633,7 +8633,7 @@
         <v>62</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>12</v>
@@ -8657,7 +8657,7 @@
       <c r="J285" s="2"/>
       <c r="K285" s="1"/>
       <c r="M285" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="286" spans="4:13" x14ac:dyDescent="0.3">
@@ -8674,7 +8674,7 @@
         <v>42</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>10</v>
@@ -8706,7 +8706,7 @@
         <v>42</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>10</v>
@@ -8735,7 +8735,7 @@
         <v>49</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>10</v>
@@ -8767,7 +8767,7 @@
         <v>42</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>10</v>
@@ -8799,7 +8799,7 @@
         <v>42</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>13</v>
@@ -8831,7 +8831,7 @@
         <v>42</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>13</v>
@@ -8863,7 +8863,7 @@
         <v>42</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>13</v>
@@ -8895,7 +8895,7 @@
         <v>42</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>13</v>
@@ -8927,7 +8927,7 @@
         <v>42</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>13</v>
@@ -8959,7 +8959,7 @@
         <v>42</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>13</v>
@@ -8988,7 +8988,7 @@
         <v>37</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>13</v>
@@ -9017,7 +9017,7 @@
         <v>39</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>13</v>
@@ -9049,7 +9049,7 @@
         <v>42</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>13</v>
@@ -9081,7 +9081,7 @@
         <v>42</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>13</v>
@@ -9113,7 +9113,7 @@
         <v>42</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>13</v>
@@ -9145,7 +9145,7 @@
         <v>42</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>13</v>
@@ -9174,7 +9174,7 @@
         <v>61</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>13</v>
@@ -9206,7 +9206,7 @@
         <v>42</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>13</v>
@@ -9235,7 +9235,7 @@
         <v>62</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>13</v>
@@ -9267,7 +9267,7 @@
         <v>42</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>10</v>
@@ -9299,7 +9299,7 @@
         <v>42</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>10</v>
@@ -9328,7 +9328,7 @@
         <v>49</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>12</v>
@@ -9352,7 +9352,7 @@
       <c r="J308" s="2"/>
       <c r="K308" s="1"/>
       <c r="M308" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="309" spans="4:13" x14ac:dyDescent="0.3">
@@ -9369,7 +9369,7 @@
         <v>42</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>10</v>
@@ -9401,7 +9401,7 @@
         <v>42</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>13</v>
@@ -9433,7 +9433,7 @@
         <v>42</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>13</v>
@@ -9465,7 +9465,7 @@
         <v>42</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>13</v>
@@ -9497,7 +9497,7 @@
         <v>42</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>13</v>
@@ -9529,7 +9529,7 @@
         <v>42</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>13</v>
@@ -9561,7 +9561,7 @@
         <v>42</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I315" s="1" t="s">
         <v>13</v>
@@ -9614,7 +9614,7 @@
       <c r="J317" s="2"/>
       <c r="K317" s="1"/>
       <c r="M317" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="318" spans="4:13" x14ac:dyDescent="0.3">
@@ -10134,7 +10134,7 @@
         <v>42</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>12</v>
@@ -10158,7 +10158,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
       <c r="M335" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="336" spans="4:13" x14ac:dyDescent="0.3">
@@ -10172,7 +10172,7 @@
         <v>37</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>10</v>
@@ -10201,7 +10201,7 @@
         <v>39</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>13</v>
@@ -10233,7 +10233,7 @@
         <v>42</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>10</v>
@@ -10265,7 +10265,7 @@
         <v>42</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>10</v>
@@ -10297,7 +10297,7 @@
         <v>42</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>10</v>
@@ -10326,7 +10326,7 @@
         <v>62</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>13</v>
@@ -10358,7 +10358,7 @@
         <v>42</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>10</v>
@@ -10387,7 +10387,7 @@
         <v>49</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>10</v>
@@ -10419,7 +10419,7 @@
         <v>42</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>13</v>
@@ -10451,7 +10451,7 @@
         <v>42</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>13</v>
@@ -10483,7 +10483,7 @@
         <v>42</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I346" s="1" t="s">
         <v>10</v>
@@ -10515,7 +10515,7 @@
         <v>42</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>10</v>
@@ -10547,7 +10547,7 @@
         <v>42</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>10</v>
@@ -10579,7 +10579,7 @@
         <v>42</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>10</v>
@@ -10611,7 +10611,7 @@
         <v>42</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>13</v>
@@ -10643,7 +10643,7 @@
         <v>42</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>13</v>
@@ -10675,7 +10675,7 @@
         <v>42</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>13</v>
@@ -10707,7 +10707,7 @@
         <v>42</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>13</v>
@@ -10739,7 +10739,7 @@
         <v>42</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I354" s="1" t="s">
         <v>10</v>
@@ -10768,7 +10768,7 @@
         <v>37</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>10</v>
@@ -10797,7 +10797,7 @@
         <v>39</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>10</v>
@@ -10829,7 +10829,7 @@
         <v>42</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I357" s="1" t="s">
         <v>13</v>
@@ -10861,7 +10861,7 @@
         <v>42</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I358" s="1" t="s">
         <v>12</v>
@@ -10885,7 +10885,7 @@
       <c r="J359" s="2"/>
       <c r="K359" s="1"/>
       <c r="M359" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="360" spans="4:13" x14ac:dyDescent="0.3">
@@ -10902,7 +10902,7 @@
         <v>42</v>
       </c>
       <c r="H360" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I360" s="1" t="s">
         <v>10</v>
@@ -10931,7 +10931,7 @@
         <v>62</v>
       </c>
       <c r="H361" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I361" s="1" t="s">
         <v>13</v>
@@ -10963,7 +10963,7 @@
         <v>42</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I362" s="1" t="s">
         <v>10</v>
@@ -10992,7 +10992,7 @@
         <v>49</v>
       </c>
       <c r="H363" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I363" s="1" t="s">
         <v>10</v>
@@ -11024,7 +11024,7 @@
         <v>42</v>
       </c>
       <c r="H364" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I364" s="1" t="s">
         <v>10</v>
@@ -11056,7 +11056,7 @@
         <v>42</v>
       </c>
       <c r="H365" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I365" s="1" t="s">
         <v>10</v>
@@ -11088,7 +11088,7 @@
         <v>42</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I366" s="1" t="s">
         <v>10</v>
@@ -11120,7 +11120,7 @@
         <v>42</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>10</v>
@@ -11152,7 +11152,7 @@
         <v>42</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>10</v>
@@ -11184,7 +11184,7 @@
         <v>42</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I369" s="1" t="s">
         <v>13</v>
@@ -11216,7 +11216,7 @@
         <v>42</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>10</v>
@@ -11248,7 +11248,7 @@
         <v>42</v>
       </c>
       <c r="H371" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I371" s="1" t="s">
         <v>13</v>
@@ -11280,7 +11280,7 @@
         <v>42</v>
       </c>
       <c r="H372" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I372" s="1" t="s">
         <v>13</v>
@@ -11312,7 +11312,7 @@
         <v>42</v>
       </c>
       <c r="H373" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I373" s="1" t="s">
         <v>13</v>
@@ -11344,7 +11344,7 @@
         <v>42</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>10</v>
@@ -11373,7 +11373,7 @@
         <v>37</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>10</v>
@@ -11402,7 +11402,7 @@
         <v>39</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>10</v>
@@ -11434,7 +11434,7 @@
         <v>42</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I377" s="1" t="s">
         <v>10</v>
@@ -11466,7 +11466,7 @@
         <v>42</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>10</v>
@@ -11495,7 +11495,7 @@
         <v>62</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>13</v>
@@ -11527,7 +11527,7 @@
         <v>42</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I380" s="1" t="s">
         <v>10</v>
@@ -11556,7 +11556,7 @@
         <v>49</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I381" s="1" t="s">
         <v>10</v>
@@ -11588,7 +11588,7 @@
         <v>42</v>
       </c>
       <c r="H382" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I382" s="1" t="s">
         <v>10</v>
@@ -11620,7 +11620,7 @@
         <v>42</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I383" s="1" t="s">
         <v>10</v>
@@ -11652,7 +11652,7 @@
         <v>42</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>10</v>
@@ -11684,7 +11684,7 @@
         <v>42</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>10</v>
@@ -11716,7 +11716,7 @@
         <v>42</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I386" s="1" t="s">
         <v>13</v>
@@ -11748,7 +11748,7 @@
         <v>42</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>13</v>
@@ -11780,7 +11780,7 @@
         <v>42</v>
       </c>
       <c r="H388" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I388" s="1" t="s">
         <v>13</v>
@@ -11812,7 +11812,7 @@
         <v>42</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I389" s="1" t="s">
         <v>13</v>
@@ -11844,7 +11844,7 @@
         <v>42</v>
       </c>
       <c r="H390" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I390" s="1" t="s">
         <v>10</v>
@@ -11873,7 +11873,7 @@
         <v>37</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I391" s="1" t="s">
         <v>10</v>
@@ -11902,7 +11902,7 @@
         <v>39</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I392" s="1" t="s">
         <v>13</v>
@@ -11934,7 +11934,7 @@
         <v>42</v>
       </c>
       <c r="H393" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I393" s="1" t="s">
         <v>10</v>
@@ -11966,7 +11966,7 @@
         <v>42</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I394" s="1" t="s">
         <v>10</v>
@@ -11995,7 +11995,7 @@
         <v>62</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I395" s="1" t="s">
         <v>13</v>
@@ -12027,7 +12027,7 @@
         <v>42</v>
       </c>
       <c r="H396" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I396" s="1" t="s">
         <v>10</v>
@@ -12056,7 +12056,7 @@
         <v>49</v>
       </c>
       <c r="H397" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I397" s="1" t="s">
         <v>10</v>
@@ -12088,7 +12088,7 @@
         <v>42</v>
       </c>
       <c r="H398" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I398" s="1" t="s">
         <v>10</v>
@@ -12120,7 +12120,7 @@
         <v>42</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I399" s="1" t="s">
         <v>10</v>
@@ -12152,7 +12152,7 @@
         <v>42</v>
       </c>
       <c r="H400" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I400" s="1" t="s">
         <v>10</v>
@@ -12184,7 +12184,7 @@
         <v>42</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I401" s="1" t="s">
         <v>10</v>
@@ -12216,7 +12216,7 @@
         <v>42</v>
       </c>
       <c r="H402" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I402" s="1" t="s">
         <v>13</v>
@@ -12248,7 +12248,7 @@
         <v>42</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I403" s="1" t="s">
         <v>13</v>
@@ -12280,7 +12280,7 @@
         <v>42</v>
       </c>
       <c r="H404" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I404" s="1" t="s">
         <v>13</v>
@@ -12312,7 +12312,7 @@
         <v>42</v>
       </c>
       <c r="H405" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I405" s="1" t="s">
         <v>13</v>
@@ -12344,7 +12344,7 @@
         <v>42</v>
       </c>
       <c r="H406" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I406" s="1" t="s">
         <v>10</v>
@@ -12373,7 +12373,7 @@
         <v>37</v>
       </c>
       <c r="H407" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I407" s="1" t="s">
         <v>10</v>
@@ -12402,7 +12402,7 @@
         <v>39</v>
       </c>
       <c r="H408" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I408" s="1" t="s">
         <v>13</v>
@@ -12434,7 +12434,7 @@
         <v>42</v>
       </c>
       <c r="H409" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I409" s="1" t="s">
         <v>13</v>
@@ -12466,7 +12466,7 @@
         <v>42</v>
       </c>
       <c r="H410" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I410" s="1" t="s">
         <v>10</v>
@@ -12495,7 +12495,7 @@
         <v>62</v>
       </c>
       <c r="H411" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I411" s="1" t="s">
         <v>13</v>
@@ -12527,7 +12527,7 @@
         <v>42</v>
       </c>
       <c r="H412" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I412" s="1" t="s">
         <v>10</v>
@@ -12556,7 +12556,7 @@
         <v>49</v>
       </c>
       <c r="H413" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I413" s="1" t="s">
         <v>10</v>
@@ -12588,7 +12588,7 @@
         <v>42</v>
       </c>
       <c r="H414" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I414" s="1" t="s">
         <v>10</v>
@@ -12620,7 +12620,7 @@
         <v>42</v>
       </c>
       <c r="H415" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I415" s="1" t="s">
         <v>10</v>
@@ -12652,7 +12652,7 @@
         <v>42</v>
       </c>
       <c r="H416" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I416" s="1" t="s">
         <v>10</v>
@@ -12684,7 +12684,7 @@
         <v>42</v>
       </c>
       <c r="H417" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I417" s="1" t="s">
         <v>14</v>
@@ -12708,7 +12708,7 @@
       <c r="J418" s="2"/>
       <c r="K418" s="1"/>
       <c r="M418" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="419" spans="4:13" x14ac:dyDescent="0.3">
@@ -12725,7 +12725,7 @@
         <v>42</v>
       </c>
       <c r="H419" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I419" s="1" t="s">
         <v>13</v>
@@ -12757,7 +12757,7 @@
         <v>42</v>
       </c>
       <c r="H420" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I420" s="1" t="s">
         <v>13</v>
@@ -12789,7 +12789,7 @@
         <v>42</v>
       </c>
       <c r="H421" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I421" s="1" t="s">
         <v>13</v>
@@ -12821,7 +12821,7 @@
         <v>42</v>
       </c>
       <c r="H422" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I422" s="1" t="s">
         <v>10</v>
@@ -12850,7 +12850,7 @@
         <v>37</v>
       </c>
       <c r="H423" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I423" s="1" t="s">
         <v>10</v>
@@ -12879,7 +12879,7 @@
         <v>39</v>
       </c>
       <c r="H424" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I424" s="1" t="s">
         <v>13</v>
@@ -12911,7 +12911,7 @@
         <v>42</v>
       </c>
       <c r="H425" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I425" s="1" t="s">
         <v>10</v>
@@ -12943,7 +12943,7 @@
         <v>42</v>
       </c>
       <c r="H426" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I426" s="1" t="s">
         <v>10</v>
@@ -12972,7 +12972,7 @@
         <v>62</v>
       </c>
       <c r="H427" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I427" s="1" t="s">
         <v>13</v>
@@ -13004,7 +13004,7 @@
         <v>42</v>
       </c>
       <c r="H428" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I428" s="1" t="s">
         <v>10</v>
@@ -13033,7 +13033,7 @@
         <v>49</v>
       </c>
       <c r="H429" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I429" s="1" t="s">
         <v>12</v>
@@ -13057,7 +13057,7 @@
       <c r="J430" s="2"/>
       <c r="K430" s="1"/>
       <c r="M430" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="431" spans="4:13" x14ac:dyDescent="0.3">
@@ -13074,7 +13074,7 @@
         <v>42</v>
       </c>
       <c r="H431" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I431" s="1" t="s">
         <v>10</v>
@@ -13106,7 +13106,7 @@
         <v>42</v>
       </c>
       <c r="H432" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I432" s="1" t="s">
         <v>10</v>
@@ -13138,7 +13138,7 @@
         <v>42</v>
       </c>
       <c r="H433" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I433" s="1" t="s">
         <v>13</v>
@@ -13170,7 +13170,7 @@
         <v>42</v>
       </c>
       <c r="H434" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I434" s="1" t="s">
         <v>13</v>
@@ -13202,7 +13202,7 @@
         <v>42</v>
       </c>
       <c r="H435" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I435" s="1" t="s">
         <v>13</v>
@@ -13234,7 +13234,7 @@
         <v>42</v>
       </c>
       <c r="H436" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I436" s="1" t="s">
         <v>13</v>
@@ -13266,7 +13266,7 @@
         <v>42</v>
       </c>
       <c r="H437" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I437" s="1" t="s">
         <v>13</v>
@@ -13298,7 +13298,7 @@
         <v>42</v>
       </c>
       <c r="H438" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I438" s="1" t="s">
         <v>10</v>
@@ -13412,7 +13412,7 @@
       <c r="J442" s="2"/>
       <c r="K442" s="1"/>
       <c r="M442" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="443" spans="4:13" x14ac:dyDescent="0.3">
@@ -13482,7 +13482,7 @@
       <c r="J445" s="2"/>
       <c r="K445" s="1"/>
       <c r="M445" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="446" spans="4:13" x14ac:dyDescent="0.3">
@@ -13813,7 +13813,7 @@
         <v>37</v>
       </c>
       <c r="H456" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I456" s="1" t="s">
         <v>13</v>
@@ -13842,7 +13842,7 @@
         <v>39</v>
       </c>
       <c r="H457" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I457" s="1" t="s">
         <v>13</v>
@@ -13874,7 +13874,7 @@
         <v>42</v>
       </c>
       <c r="H458" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I458" s="1" t="s">
         <v>13</v>
@@ -13906,7 +13906,7 @@
         <v>42</v>
       </c>
       <c r="H459" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I459" s="1" t="s">
         <v>13</v>
@@ -13935,7 +13935,7 @@
         <v>62</v>
       </c>
       <c r="H460" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I460" s="1" t="s">
         <v>13</v>
@@ -13967,7 +13967,7 @@
         <v>42</v>
       </c>
       <c r="H461" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I461" s="1" t="s">
         <v>10</v>
@@ -13996,7 +13996,7 @@
         <v>49</v>
       </c>
       <c r="H462" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I462" s="1" t="s">
         <v>10</v>
@@ -14028,7 +14028,7 @@
         <v>42</v>
       </c>
       <c r="H463" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I463" s="1" t="s">
         <v>13</v>
@@ -14060,7 +14060,7 @@
         <v>42</v>
       </c>
       <c r="H464" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I464" s="1" t="s">
         <v>10</v>
@@ -14092,7 +14092,7 @@
         <v>42</v>
       </c>
       <c r="H465" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I465" s="1" t="s">
         <v>13</v>
@@ -14124,7 +14124,7 @@
         <v>42</v>
       </c>
       <c r="H466" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I466" s="1" t="s">
         <v>13</v>
@@ -14156,7 +14156,7 @@
         <v>42</v>
       </c>
       <c r="H467" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I467" s="1" t="s">
         <v>13</v>
@@ -14188,7 +14188,7 @@
         <v>42</v>
       </c>
       <c r="H468" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I468" s="1" t="s">
         <v>13</v>
@@ -14220,7 +14220,7 @@
         <v>42</v>
       </c>
       <c r="H469" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I469" s="1" t="s">
         <v>13</v>
@@ -14252,7 +14252,7 @@
         <v>42</v>
       </c>
       <c r="H470" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I470" s="1" t="s">
         <v>10</v>
@@ -14281,7 +14281,7 @@
         <v>37</v>
       </c>
       <c r="H471" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I471" s="1" t="s">
         <v>13</v>
@@ -14310,7 +14310,7 @@
         <v>39</v>
       </c>
       <c r="H472" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I472" s="1" t="s">
         <v>13</v>
@@ -14342,7 +14342,7 @@
         <v>42</v>
       </c>
       <c r="H473" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I473" s="1" t="s">
         <v>13</v>
@@ -14374,7 +14374,7 @@
         <v>42</v>
       </c>
       <c r="H474" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I474" s="1" t="s">
         <v>13</v>
@@ -14403,7 +14403,7 @@
         <v>62</v>
       </c>
       <c r="H475" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I475" s="1" t="s">
         <v>13</v>
@@ -14435,7 +14435,7 @@
         <v>42</v>
       </c>
       <c r="H476" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I476" s="1" t="s">
         <v>10</v>
@@ -14464,7 +14464,7 @@
         <v>49</v>
       </c>
       <c r="H477" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I477" s="1" t="s">
         <v>10</v>
@@ -14496,7 +14496,7 @@
         <v>42</v>
       </c>
       <c r="H478" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I478" s="1" t="s">
         <v>13</v>
@@ -14528,7 +14528,7 @@
         <v>42</v>
       </c>
       <c r="H479" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I479" s="1" t="s">
         <v>13</v>
@@ -14560,7 +14560,7 @@
         <v>42</v>
       </c>
       <c r="H480" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I480" s="1" t="s">
         <v>10</v>
@@ -14592,7 +14592,7 @@
         <v>42</v>
       </c>
       <c r="H481" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I481" s="1" t="s">
         <v>14</v>
@@ -14616,7 +14616,7 @@
       <c r="J482" s="2"/>
       <c r="K482" s="1"/>
       <c r="M482" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="483" spans="4:13" x14ac:dyDescent="0.3">
@@ -14633,7 +14633,7 @@
         <v>42</v>
       </c>
       <c r="H483" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I483" s="1" t="s">
         <v>13</v>
@@ -14665,7 +14665,7 @@
         <v>42</v>
       </c>
       <c r="H484" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I484" s="1" t="s">
         <v>13</v>
@@ -14697,7 +14697,7 @@
         <v>42</v>
       </c>
       <c r="H485" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I485" s="1" t="s">
         <v>13</v>
@@ -14729,7 +14729,7 @@
         <v>42</v>
       </c>
       <c r="H486" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I486" s="1" t="s">
         <v>10</v>
@@ -14758,7 +14758,7 @@
         <v>37</v>
       </c>
       <c r="H487" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I487" s="1" t="s">
         <v>13</v>
@@ -14787,7 +14787,7 @@
         <v>39</v>
       </c>
       <c r="H488" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I488" s="1" t="s">
         <v>13</v>
@@ -14819,7 +14819,7 @@
         <v>42</v>
       </c>
       <c r="H489" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I489" s="1" t="s">
         <v>13</v>
@@ -14851,7 +14851,7 @@
         <v>42</v>
       </c>
       <c r="H490" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I490" s="1" t="s">
         <v>10</v>
@@ -14880,7 +14880,7 @@
         <v>62</v>
       </c>
       <c r="H491" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I491" s="1" t="s">
         <v>13</v>
@@ -14912,7 +14912,7 @@
         <v>42</v>
       </c>
       <c r="H492" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I492" s="1" t="s">
         <v>10</v>
@@ -14941,7 +14941,7 @@
         <v>49</v>
       </c>
       <c r="H493" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I493" s="1" t="s">
         <v>12</v>
@@ -14965,7 +14965,7 @@
       <c r="J494" s="2"/>
       <c r="K494" s="1"/>
       <c r="M494" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="495" spans="4:13" x14ac:dyDescent="0.3">
@@ -14982,7 +14982,7 @@
         <v>42</v>
       </c>
       <c r="H495" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I495" s="1" t="s">
         <v>10</v>
@@ -15014,7 +15014,7 @@
         <v>42</v>
       </c>
       <c r="H496" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I496" s="1" t="s">
         <v>12</v>
@@ -15038,7 +15038,7 @@
       <c r="J497" s="2"/>
       <c r="K497" s="1"/>
       <c r="M497" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="498" spans="4:13" x14ac:dyDescent="0.3">
@@ -15055,7 +15055,7 @@
         <v>42</v>
       </c>
       <c r="H498" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I498" s="1" t="s">
         <v>10</v>
@@ -15087,7 +15087,7 @@
         <v>42</v>
       </c>
       <c r="H499" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I499" s="1" t="s">
         <v>10</v>
@@ -15119,7 +15119,7 @@
         <v>42</v>
       </c>
       <c r="H500" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I500" s="1" t="s">
         <v>13</v>
@@ -15151,7 +15151,7 @@
         <v>42</v>
       </c>
       <c r="H501" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I501" s="1" t="s">
         <v>13</v>
@@ -15183,7 +15183,7 @@
         <v>42</v>
       </c>
       <c r="H502" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I502" s="1" t="s">
         <v>13</v>
@@ -15215,7 +15215,7 @@
         <v>42</v>
       </c>
       <c r="H503" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I503" s="1" t="s">
         <v>10</v>
@@ -15404,7 +15404,7 @@
         <v>49</v>
       </c>
       <c r="H509" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I509" s="1" t="s">
         <v>10</v>
@@ -15436,7 +15436,7 @@
         <v>42</v>
       </c>
       <c r="H510" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I510" s="1" t="s">
         <v>10</v>
@@ -15465,7 +15465,7 @@
         <v>37</v>
       </c>
       <c r="H511" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I511" s="1" t="s">
         <v>13</v>
@@ -15494,7 +15494,7 @@
         <v>39</v>
       </c>
       <c r="H512" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I512" s="1" t="s">
         <v>13</v>
@@ -15526,7 +15526,7 @@
         <v>42</v>
       </c>
       <c r="H513" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I513" s="1" t="s">
         <v>13</v>
@@ -15558,7 +15558,7 @@
         <v>42</v>
       </c>
       <c r="H514" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I514" s="1" t="s">
         <v>10</v>
@@ -15587,7 +15587,7 @@
         <v>62</v>
       </c>
       <c r="H515" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I515" s="1" t="s">
         <v>13</v>
@@ -15619,7 +15619,7 @@
         <v>42</v>
       </c>
       <c r="H516" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I516" s="1" t="s">
         <v>10</v>
@@ -15651,7 +15651,7 @@
         <v>42</v>
       </c>
       <c r="H517" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I517" s="1" t="s">
         <v>10</v>
@@ -15683,7 +15683,7 @@
         <v>42</v>
       </c>
       <c r="H518" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I518" s="1" t="s">
         <v>10</v>
@@ -15715,7 +15715,7 @@
         <v>42</v>
       </c>
       <c r="H519" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I519" s="1" t="s">
         <v>10</v>
@@ -15747,7 +15747,7 @@
         <v>42</v>
       </c>
       <c r="H520" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I520" s="1" t="s">
         <v>13</v>
@@ -15779,7 +15779,7 @@
         <v>42</v>
       </c>
       <c r="H521" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I521" s="1" t="s">
         <v>10</v>
@@ -17426,6 +17426,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -17500,6 +17501,7 @@
     <row r="807" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H807" s="2"/>
       <c r="I807" s="1"/>
+      <c r="J807" s="2"/>
       <c r="K807" s="1"/>
     </row>
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
@@ -51008,7 +51010,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\mericles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C0F6BD5-F9A5-4F0D-9414-0048F77E05E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0038A920-6374-4A61-B094-954028CF2C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2766" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="66">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,10 +86,16 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Speed Management</t>
+    <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
     <t>Vehicle Inspections</t>
+  </si>
+  <si>
+    <t>Work Zone Safety</t>
   </si>
   <si>
     <t>Winter Weather</t>
@@ -101,28 +107,28 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Space Management-Big 5</t>
+    <t>Distracted Driving</t>
   </si>
   <si>
-    <t>Distracted Driving</t>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Alert Driving</t>
   </si>
   <si>
-    <t>Driver Health</t>
-  </si>
-  <si>
-    <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
+    <t>Speed Management</t>
   </si>
   <si>
     <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
+    <t>Space Management-Big 5</t>
+  </si>
+  <si>
     <t>Alert Driving: Big Three</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
@@ -131,16 +137,10 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
     <t>Scene of an Accident</t>
   </si>
   <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
-  </si>
-  <si>
-    <t>Camera Event Management Orientation for Drivers</t>
   </si>
   <si>
     <t>DOT Reasonable Suspicion: The Power of the Three R’s</t>
@@ -610,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -750,7 +750,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="1"/>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
@@ -791,7 +791,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="1"/>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
@@ -832,7 +832,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="1"/>
       <c r="M9" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
@@ -873,7 +873,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="1"/>
       <c r="M11" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
@@ -1135,7 +1135,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="1"/>
       <c r="M20" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
@@ -1208,7 +1208,7 @@
       <c r="J23" s="2"/>
       <c r="K23" s="1"/>
       <c r="M23" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
@@ -1281,7 +1281,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="1"/>
       <c r="M26" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
@@ -1441,7 +1441,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="1"/>
       <c r="M32" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
@@ -1514,7 +1514,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="1"/>
       <c r="M35" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
@@ -1651,7 +1651,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="1"/>
       <c r="M40" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
@@ -1721,7 +1721,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="1"/>
       <c r="M43" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
@@ -1794,7 +1794,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="1"/>
       <c r="M46" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.3">
@@ -1995,7 +1995,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="1"/>
       <c r="M53" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
@@ -2065,7 +2065,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="1"/>
       <c r="M56" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
@@ -2196,7 +2196,7 @@
       <c r="J61" s="2"/>
       <c r="K61" s="1"/>
       <c r="M61" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
@@ -2237,7 +2237,7 @@
       <c r="J63" s="2"/>
       <c r="K63" s="1"/>
       <c r="M63" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
@@ -2278,7 +2278,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="1"/>
       <c r="M65" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
@@ -2476,7 +2476,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="1"/>
       <c r="M72" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
@@ -2549,7 +2549,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="1"/>
       <c r="M75" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
@@ -2622,7 +2622,7 @@
       <c r="J78" s="2"/>
       <c r="K78" s="1"/>
       <c r="M78" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
@@ -2695,7 +2695,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="1"/>
       <c r="M81" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
@@ -2741,7 +2741,7 @@
         <v>37</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>12</v>
@@ -2765,7 +2765,7 @@
       <c r="J84" s="2"/>
       <c r="K84" s="1"/>
       <c r="M84" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
@@ -2782,7 +2782,7 @@
         <v>42</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>13</v>
@@ -2814,7 +2814,7 @@
         <v>42</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>12</v>
@@ -2838,7 +2838,7 @@
       <c r="J87" s="2"/>
       <c r="K87" s="1"/>
       <c r="M87" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
@@ -2855,7 +2855,7 @@
         <v>42</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -2887,7 +2887,7 @@
         <v>42</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -2919,7 +2919,7 @@
         <v>42</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>13</v>
@@ -2948,7 +2948,7 @@
         <v>49</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>13</v>
@@ -2980,7 +2980,7 @@
         <v>42</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>13</v>
@@ -3012,7 +3012,7 @@
         <v>42</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>13</v>
@@ -3044,7 +3044,7 @@
         <v>42</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>13</v>
@@ -3076,7 +3076,7 @@
         <v>42</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>13</v>
@@ -3108,7 +3108,7 @@
         <v>42</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>13</v>
@@ -3140,7 +3140,7 @@
         <v>42</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>13</v>
@@ -3172,7 +3172,7 @@
         <v>42</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>12</v>
@@ -3196,7 +3196,7 @@
       <c r="J99" s="2"/>
       <c r="K99" s="1"/>
       <c r="M99" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
@@ -3213,7 +3213,7 @@
         <v>42</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>14</v>
@@ -3237,7 +3237,7 @@
       <c r="J101" s="2"/>
       <c r="K101" s="1"/>
       <c r="M101" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.3">
@@ -3251,7 +3251,7 @@
         <v>37</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>13</v>
@@ -3280,7 +3280,7 @@
         <v>39</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3309,7 +3309,7 @@
         <v>40</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>10</v>
@@ -3341,7 +3341,7 @@
         <v>42</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>13</v>
@@ -3373,7 +3373,7 @@
         <v>42</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>10</v>
@@ -3405,7 +3405,7 @@
         <v>42</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>13</v>
@@ -3437,7 +3437,7 @@
         <v>42</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>13</v>
@@ -3469,7 +3469,7 @@
         <v>42</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>13</v>
@@ -3501,7 +3501,7 @@
         <v>42</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>10</v>
@@ -3533,7 +3533,7 @@
         <v>42</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>10</v>
@@ -3565,7 +3565,7 @@
         <v>42</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>12</v>
@@ -3589,7 +3589,7 @@
       <c r="J113" s="2"/>
       <c r="K113" s="1"/>
       <c r="M113" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
@@ -3603,7 +3603,7 @@
         <v>49</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>13</v>
@@ -3635,7 +3635,7 @@
         <v>42</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>13</v>
@@ -3667,7 +3667,7 @@
         <v>42</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>12</v>
@@ -3691,7 +3691,7 @@
       <c r="J117" s="2"/>
       <c r="K117" s="1"/>
       <c r="M117" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118" spans="4:13" x14ac:dyDescent="0.3">
@@ -3708,7 +3708,7 @@
         <v>42</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>13</v>
@@ -3740,7 +3740,7 @@
         <v>42</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>13</v>
@@ -3772,7 +3772,7 @@
         <v>42</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>10</v>
@@ -3804,7 +3804,7 @@
         <v>42</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>13</v>
@@ -3836,7 +3836,7 @@
         <v>42</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>13</v>
@@ -3868,7 +3868,7 @@
         <v>42</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>13</v>
@@ -3897,7 +3897,7 @@
         <v>37</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>13</v>
@@ -3926,7 +3926,7 @@
         <v>39</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>13</v>
@@ -3955,7 +3955,7 @@
         <v>40</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -3987,7 +3987,7 @@
         <v>42</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>14</v>
@@ -4011,7 +4011,7 @@
       <c r="J128" s="2"/>
       <c r="K128" s="1"/>
       <c r="M128" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
@@ -4028,7 +4028,7 @@
         <v>42</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>10</v>
@@ -4060,7 +4060,7 @@
         <v>42</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4092,7 +4092,7 @@
         <v>42</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>13</v>
@@ -4124,7 +4124,7 @@
         <v>42</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>13</v>
@@ -4156,7 +4156,7 @@
         <v>42</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>13</v>
@@ -4188,7 +4188,7 @@
         <v>42</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4220,7 +4220,7 @@
         <v>42</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>13</v>
@@ -4249,7 +4249,7 @@
         <v>49</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>13</v>
@@ -4281,7 +4281,7 @@
         <v>42</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>13</v>
@@ -4313,7 +4313,7 @@
         <v>42</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>13</v>
@@ -4345,7 +4345,7 @@
         <v>42</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>13</v>
@@ -4377,7 +4377,7 @@
         <v>42</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>14</v>
@@ -4401,7 +4401,7 @@
       <c r="J141" s="2"/>
       <c r="K141" s="1"/>
       <c r="M141" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="142" spans="4:13" x14ac:dyDescent="0.3">
@@ -4418,7 +4418,7 @@
         <v>42</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>13</v>
@@ -4450,7 +4450,7 @@
         <v>42</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>13</v>
@@ -4482,7 +4482,7 @@
         <v>42</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>13</v>
@@ -4514,7 +4514,7 @@
         <v>42</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>13</v>
@@ -4543,7 +4543,7 @@
         <v>37</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>13</v>
@@ -4572,7 +4572,7 @@
         <v>39</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>13</v>
@@ -4601,7 +4601,7 @@
         <v>40</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>13</v>
@@ -4633,7 +4633,7 @@
         <v>42</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>13</v>
@@ -4665,7 +4665,7 @@
         <v>42</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>13</v>
@@ -4697,7 +4697,7 @@
         <v>42</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>13</v>
@@ -4729,7 +4729,7 @@
         <v>42</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>13</v>
@@ -4761,7 +4761,7 @@
         <v>42</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>13</v>
@@ -4793,7 +4793,7 @@
         <v>42</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>13</v>
@@ -4825,7 +4825,7 @@
         <v>42</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>10</v>
@@ -4857,7 +4857,7 @@
         <v>42</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>13</v>
@@ -4886,7 +4886,7 @@
         <v>49</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>13</v>
@@ -4918,7 +4918,7 @@
         <v>42</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>13</v>
@@ -4950,7 +4950,7 @@
         <v>42</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>13</v>
@@ -4982,7 +4982,7 @@
         <v>42</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>13</v>
@@ -5014,7 +5014,7 @@
         <v>42</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>12</v>
@@ -5038,7 +5038,7 @@
       <c r="J162" s="2"/>
       <c r="K162" s="1"/>
       <c r="M162" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="163" spans="4:13" x14ac:dyDescent="0.3">
@@ -5055,7 +5055,7 @@
         <v>42</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>10</v>
@@ -5087,7 +5087,7 @@
         <v>42</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>13</v>
@@ -5119,7 +5119,7 @@
         <v>42</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>13</v>
@@ -5151,7 +5151,7 @@
         <v>42</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>13</v>
@@ -5180,7 +5180,7 @@
         <v>37</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>13</v>
@@ -5209,7 +5209,7 @@
         <v>39</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>10</v>
@@ -5238,7 +5238,7 @@
         <v>40</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>13</v>
@@ -5270,7 +5270,7 @@
         <v>42</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>10</v>
@@ -5302,7 +5302,7 @@
         <v>42</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>10</v>
@@ -5334,7 +5334,7 @@
         <v>42</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>10</v>
@@ -5366,7 +5366,7 @@
         <v>42</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>10</v>
@@ -5398,7 +5398,7 @@
         <v>42</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>10</v>
@@ -5430,7 +5430,7 @@
         <v>42</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>13</v>
@@ -5462,7 +5462,7 @@
         <v>42</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>10</v>
@@ -5494,7 +5494,7 @@
         <v>42</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>10</v>
@@ -5523,7 +5523,7 @@
         <v>49</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>10</v>
@@ -5555,7 +5555,7 @@
         <v>42</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>10</v>
@@ -5587,7 +5587,7 @@
         <v>42</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>12</v>
@@ -5611,7 +5611,7 @@
       <c r="J181" s="2"/>
       <c r="K181" s="1"/>
       <c r="M181" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="182" spans="4:13" x14ac:dyDescent="0.3">
@@ -5628,7 +5628,7 @@
         <v>42</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>13</v>
@@ -5660,7 +5660,7 @@
         <v>42</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>10</v>
@@ -5692,7 +5692,7 @@
         <v>42</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>10</v>
@@ -5724,7 +5724,7 @@
         <v>42</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>13</v>
@@ -5756,7 +5756,7 @@
         <v>42</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>13</v>
@@ -5788,7 +5788,7 @@
         <v>42</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>10</v>
@@ -5817,7 +5817,7 @@
         <v>37</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>13</v>
@@ -5846,7 +5846,7 @@
         <v>39</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>10</v>
@@ -5875,7 +5875,7 @@
         <v>40</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>13</v>
@@ -5907,7 +5907,7 @@
         <v>42</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>10</v>
@@ -5939,7 +5939,7 @@
         <v>42</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>13</v>
@@ -5971,7 +5971,7 @@
         <v>42</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>13</v>
@@ -6003,7 +6003,7 @@
         <v>42</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>10</v>
@@ -6032,7 +6032,7 @@
         <v>61</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>10</v>
@@ -6064,7 +6064,7 @@
         <v>42</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>13</v>
@@ -6093,7 +6093,7 @@
         <v>62</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>14</v>
@@ -6117,7 +6117,7 @@
       <c r="J198" s="2"/>
       <c r="K198" s="1"/>
       <c r="M198" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="199" spans="4:13" x14ac:dyDescent="0.3">
@@ -6134,7 +6134,7 @@
         <v>42</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>10</v>
@@ -6166,7 +6166,7 @@
         <v>42</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>10</v>
@@ -6195,7 +6195,7 @@
         <v>49</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>10</v>
@@ -6227,7 +6227,7 @@
         <v>42</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>10</v>
@@ -6259,7 +6259,7 @@
         <v>42</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>10</v>
@@ -6291,7 +6291,7 @@
         <v>42</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>13</v>
@@ -6323,7 +6323,7 @@
         <v>42</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>12</v>
@@ -6347,7 +6347,7 @@
       <c r="J206" s="2"/>
       <c r="K206" s="1"/>
       <c r="M206" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="207" spans="4:13" x14ac:dyDescent="0.3">
@@ -6364,7 +6364,7 @@
         <v>42</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>13</v>
@@ -6396,7 +6396,7 @@
         <v>42</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>13</v>
@@ -6428,7 +6428,7 @@
         <v>42</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>13</v>
@@ -6460,7 +6460,7 @@
         <v>42</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>10</v>
@@ -6492,7 +6492,7 @@
         <v>42</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>13</v>
@@ -6521,7 +6521,7 @@
         <v>37</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>13</v>
@@ -6550,7 +6550,7 @@
         <v>39</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>10</v>
@@ -6582,7 +6582,7 @@
         <v>42</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>10</v>
@@ -6614,7 +6614,7 @@
         <v>42</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>13</v>
@@ -6646,7 +6646,7 @@
         <v>42</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>10</v>
@@ -6678,7 +6678,7 @@
         <v>42</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>10</v>
@@ -6707,7 +6707,7 @@
         <v>61</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>13</v>
@@ -6739,7 +6739,7 @@
         <v>42</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>13</v>
@@ -6768,7 +6768,7 @@
         <v>62</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>12</v>
@@ -6792,7 +6792,7 @@
       <c r="J221" s="2"/>
       <c r="K221" s="1"/>
       <c r="M221" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="222" spans="4:13" x14ac:dyDescent="0.3">
@@ -6809,7 +6809,7 @@
         <v>42</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>10</v>
@@ -6841,7 +6841,7 @@
         <v>42</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>13</v>
@@ -6870,7 +6870,7 @@
         <v>49</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>13</v>
@@ -6902,7 +6902,7 @@
         <v>42</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>12</v>
@@ -6926,7 +6926,7 @@
       <c r="J226" s="2"/>
       <c r="K226" s="1"/>
       <c r="M226" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="227" spans="4:13" x14ac:dyDescent="0.3">
@@ -6943,7 +6943,7 @@
         <v>42</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>13</v>
@@ -6975,7 +6975,7 @@
         <v>42</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>13</v>
@@ -7007,7 +7007,7 @@
         <v>42</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>10</v>
@@ -7039,7 +7039,7 @@
         <v>42</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>10</v>
@@ -7071,7 +7071,7 @@
         <v>42</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>13</v>
@@ -7103,7 +7103,7 @@
         <v>42</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>13</v>
@@ -7135,7 +7135,7 @@
         <v>42</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>13</v>
@@ -7164,7 +7164,7 @@
         <v>37</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>13</v>
@@ -7193,7 +7193,7 @@
         <v>39</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>12</v>
@@ -7217,7 +7217,7 @@
       <c r="J236" s="2"/>
       <c r="K236" s="1"/>
       <c r="M236" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="237" spans="4:13" x14ac:dyDescent="0.3">
@@ -7234,7 +7234,7 @@
         <v>42</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>13</v>
@@ -7266,7 +7266,7 @@
         <v>42</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>13</v>
@@ -7298,7 +7298,7 @@
         <v>42</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>13</v>
@@ -7330,7 +7330,7 @@
         <v>42</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>13</v>
@@ -7359,7 +7359,7 @@
         <v>61</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>12</v>
@@ -7383,7 +7383,7 @@
       <c r="J242" s="2"/>
       <c r="K242" s="1"/>
       <c r="M242" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="243" spans="4:13" x14ac:dyDescent="0.3">
@@ -7400,7 +7400,7 @@
         <v>42</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>13</v>
@@ -7429,7 +7429,7 @@
         <v>62</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>12</v>
@@ -7453,7 +7453,7 @@
       <c r="J245" s="2"/>
       <c r="K245" s="1"/>
       <c r="M245" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="246" spans="4:13" x14ac:dyDescent="0.3">
@@ -7470,7 +7470,7 @@
         <v>42</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>10</v>
@@ -7502,7 +7502,7 @@
         <v>42</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>10</v>
@@ -7531,7 +7531,7 @@
         <v>49</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>10</v>
@@ -7563,7 +7563,7 @@
         <v>42</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>10</v>
@@ -7595,7 +7595,7 @@
         <v>42</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>13</v>
@@ -7627,7 +7627,7 @@
         <v>42</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>13</v>
@@ -7659,7 +7659,7 @@
         <v>42</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7691,7 +7691,7 @@
         <v>42</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>13</v>
@@ -7723,7 +7723,7 @@
         <v>42</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>13</v>
@@ -7755,7 +7755,7 @@
         <v>42</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>10</v>
@@ -7784,7 +7784,7 @@
         <v>37</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>13</v>
@@ -7813,7 +7813,7 @@
         <v>39</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>10</v>
@@ -7845,7 +7845,7 @@
         <v>42</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>13</v>
@@ -7877,7 +7877,7 @@
         <v>42</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>13</v>
@@ -7909,7 +7909,7 @@
         <v>42</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>13</v>
@@ -7941,7 +7941,7 @@
         <v>42</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>10</v>
@@ -7970,7 +7970,7 @@
         <v>61</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>13</v>
@@ -8002,7 +8002,7 @@
         <v>42</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>13</v>
@@ -8031,7 +8031,7 @@
         <v>62</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>13</v>
@@ -8063,7 +8063,7 @@
         <v>42</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>10</v>
@@ -8095,7 +8095,7 @@
         <v>42</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>10</v>
@@ -8124,7 +8124,7 @@
         <v>49</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>10</v>
@@ -8156,7 +8156,7 @@
         <v>42</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>10</v>
@@ -8188,7 +8188,7 @@
         <v>42</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>13</v>
@@ -8220,7 +8220,7 @@
         <v>42</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>13</v>
@@ -8252,7 +8252,7 @@
         <v>42</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>13</v>
@@ -8284,7 +8284,7 @@
         <v>42</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>13</v>
@@ -8316,7 +8316,7 @@
         <v>42</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>13</v>
@@ -8348,7 +8348,7 @@
         <v>42</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>13</v>
@@ -8401,7 +8401,7 @@
       <c r="J276" s="2"/>
       <c r="K276" s="1"/>
       <c r="M276" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="277" spans="4:13" x14ac:dyDescent="0.3">
@@ -8657,7 +8657,7 @@
       <c r="J285" s="2"/>
       <c r="K285" s="1"/>
       <c r="M285" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="286" spans="4:13" x14ac:dyDescent="0.3">
@@ -8988,7 +8988,7 @@
         <v>37</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>13</v>
@@ -9017,7 +9017,7 @@
         <v>39</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>13</v>
@@ -9049,7 +9049,7 @@
         <v>42</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>13</v>
@@ -9081,7 +9081,7 @@
         <v>42</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>13</v>
@@ -9113,7 +9113,7 @@
         <v>42</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>13</v>
@@ -9145,7 +9145,7 @@
         <v>42</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>13</v>
@@ -9174,7 +9174,7 @@
         <v>61</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>13</v>
@@ -9206,7 +9206,7 @@
         <v>42</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>13</v>
@@ -9235,7 +9235,7 @@
         <v>62</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>13</v>
@@ -9267,7 +9267,7 @@
         <v>42</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>10</v>
@@ -9299,7 +9299,7 @@
         <v>42</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>10</v>
@@ -9328,7 +9328,7 @@
         <v>49</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>12</v>
@@ -9352,7 +9352,7 @@
       <c r="J308" s="2"/>
       <c r="K308" s="1"/>
       <c r="M308" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="309" spans="4:13" x14ac:dyDescent="0.3">
@@ -9369,7 +9369,7 @@
         <v>42</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>10</v>
@@ -9401,7 +9401,7 @@
         <v>42</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>13</v>
@@ -9433,7 +9433,7 @@
         <v>42</v>
       </c>
       <c r="H311" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I311" s="1" t="s">
         <v>13</v>
@@ -9465,7 +9465,7 @@
         <v>42</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>13</v>
@@ -9497,7 +9497,7 @@
         <v>42</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>13</v>
@@ -9529,7 +9529,7 @@
         <v>42</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>13</v>
@@ -9561,7 +9561,7 @@
         <v>42</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I315" s="1" t="s">
         <v>13</v>
@@ -9590,7 +9590,7 @@
         <v>37</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>12</v>
@@ -9614,7 +9614,7 @@
       <c r="J317" s="2"/>
       <c r="K317" s="1"/>
       <c r="M317" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="318" spans="4:13" x14ac:dyDescent="0.3">
@@ -9628,7 +9628,7 @@
         <v>39</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>10</v>
@@ -9660,7 +9660,7 @@
         <v>42</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>13</v>
@@ -9692,7 +9692,7 @@
         <v>42</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>10</v>
@@ -9724,7 +9724,7 @@
         <v>42</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>10</v>
@@ -9753,7 +9753,7 @@
         <v>62</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>13</v>
@@ -9785,7 +9785,7 @@
         <v>42</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I323" s="1" t="s">
         <v>10</v>
@@ -9814,7 +9814,7 @@
         <v>49</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>10</v>
@@ -9846,7 +9846,7 @@
         <v>42</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>10</v>
@@ -9878,7 +9878,7 @@
         <v>42</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>13</v>
@@ -9910,7 +9910,7 @@
         <v>42</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I327" s="1" t="s">
         <v>10</v>
@@ -9942,7 +9942,7 @@
         <v>42</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>13</v>
@@ -9974,7 +9974,7 @@
         <v>42</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>13</v>
@@ -10006,7 +10006,7 @@
         <v>42</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>13</v>
@@ -10038,7 +10038,7 @@
         <v>42</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>13</v>
@@ -10070,7 +10070,7 @@
         <v>42</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>13</v>
@@ -10102,7 +10102,7 @@
         <v>42</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>13</v>
@@ -10158,7 +10158,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
       <c r="M335" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="336" spans="4:13" x14ac:dyDescent="0.3">
@@ -10172,7 +10172,7 @@
         <v>37</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>10</v>
@@ -10201,7 +10201,7 @@
         <v>39</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>13</v>
@@ -10233,7 +10233,7 @@
         <v>42</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>10</v>
@@ -10265,7 +10265,7 @@
         <v>42</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>10</v>
@@ -10297,7 +10297,7 @@
         <v>42</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I340" s="1" t="s">
         <v>10</v>
@@ -10326,7 +10326,7 @@
         <v>62</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>13</v>
@@ -10358,7 +10358,7 @@
         <v>42</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>10</v>
@@ -10387,7 +10387,7 @@
         <v>49</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>10</v>
@@ -10419,7 +10419,7 @@
         <v>42</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>13</v>
@@ -10451,7 +10451,7 @@
         <v>42</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>13</v>
@@ -10483,7 +10483,7 @@
         <v>42</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I346" s="1" t="s">
         <v>10</v>
@@ -10515,7 +10515,7 @@
         <v>42</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>10</v>
@@ -10547,7 +10547,7 @@
         <v>42</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>10</v>
@@ -10579,7 +10579,7 @@
         <v>42</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>10</v>
@@ -10611,7 +10611,7 @@
         <v>42</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>13</v>
@@ -10643,7 +10643,7 @@
         <v>42</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I351" s="1" t="s">
         <v>13</v>
@@ -10675,7 +10675,7 @@
         <v>42</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>13</v>
@@ -10707,7 +10707,7 @@
         <v>42</v>
       </c>
       <c r="H353" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I353" s="1" t="s">
         <v>13</v>
@@ -10739,7 +10739,7 @@
         <v>42</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I354" s="1" t="s">
         <v>10</v>
@@ -10885,7 +10885,7 @@
       <c r="J359" s="2"/>
       <c r="K359" s="1"/>
       <c r="M359" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="360" spans="4:13" x14ac:dyDescent="0.3">
@@ -11373,7 +11373,7 @@
         <v>37</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>10</v>
@@ -11402,7 +11402,7 @@
         <v>39</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>10</v>
@@ -11434,7 +11434,7 @@
         <v>42</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I377" s="1" t="s">
         <v>10</v>
@@ -11466,7 +11466,7 @@
         <v>42</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>10</v>
@@ -11495,7 +11495,7 @@
         <v>62</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>13</v>
@@ -11527,7 +11527,7 @@
         <v>42</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I380" s="1" t="s">
         <v>10</v>
@@ -11556,7 +11556,7 @@
         <v>49</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I381" s="1" t="s">
         <v>10</v>
@@ -11588,7 +11588,7 @@
         <v>42</v>
       </c>
       <c r="H382" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I382" s="1" t="s">
         <v>10</v>
@@ -11620,7 +11620,7 @@
         <v>42</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I383" s="1" t="s">
         <v>10</v>
@@ -11652,7 +11652,7 @@
         <v>42</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>10</v>
@@ -11684,7 +11684,7 @@
         <v>42</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>10</v>
@@ -11716,7 +11716,7 @@
         <v>42</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I386" s="1" t="s">
         <v>13</v>
@@ -11748,7 +11748,7 @@
         <v>42</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>13</v>
@@ -11780,7 +11780,7 @@
         <v>42</v>
       </c>
       <c r="H388" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I388" s="1" t="s">
         <v>13</v>
@@ -11812,7 +11812,7 @@
         <v>42</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I389" s="1" t="s">
         <v>13</v>
@@ -11844,7 +11844,7 @@
         <v>42</v>
       </c>
       <c r="H390" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I390" s="1" t="s">
         <v>10</v>
@@ -11873,7 +11873,7 @@
         <v>37</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I391" s="1" t="s">
         <v>10</v>
@@ -11902,7 +11902,7 @@
         <v>39</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I392" s="1" t="s">
         <v>13</v>
@@ -11934,7 +11934,7 @@
         <v>42</v>
       </c>
       <c r="H393" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I393" s="1" t="s">
         <v>10</v>
@@ -11966,7 +11966,7 @@
         <v>42</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I394" s="1" t="s">
         <v>10</v>
@@ -11995,7 +11995,7 @@
         <v>62</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I395" s="1" t="s">
         <v>13</v>
@@ -12027,7 +12027,7 @@
         <v>42</v>
       </c>
       <c r="H396" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I396" s="1" t="s">
         <v>10</v>
@@ -12056,7 +12056,7 @@
         <v>49</v>
       </c>
       <c r="H397" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I397" s="1" t="s">
         <v>10</v>
@@ -12088,7 +12088,7 @@
         <v>42</v>
       </c>
       <c r="H398" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I398" s="1" t="s">
         <v>10</v>
@@ -12120,7 +12120,7 @@
         <v>42</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I399" s="1" t="s">
         <v>10</v>
@@ -12152,7 +12152,7 @@
         <v>42</v>
       </c>
       <c r="H400" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I400" s="1" t="s">
         <v>10</v>
@@ -12184,7 +12184,7 @@
         <v>42</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I401" s="1" t="s">
         <v>10</v>
@@ -12216,7 +12216,7 @@
         <v>42</v>
       </c>
       <c r="H402" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I402" s="1" t="s">
         <v>13</v>
@@ -12248,7 +12248,7 @@
         <v>42</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I403" s="1" t="s">
         <v>13</v>
@@ -12280,7 +12280,7 @@
         <v>42</v>
       </c>
       <c r="H404" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I404" s="1" t="s">
         <v>13</v>
@@ -12312,7 +12312,7 @@
         <v>42</v>
       </c>
       <c r="H405" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I405" s="1" t="s">
         <v>13</v>
@@ -12344,7 +12344,7 @@
         <v>42</v>
       </c>
       <c r="H406" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I406" s="1" t="s">
         <v>10</v>
@@ -12373,7 +12373,7 @@
         <v>37</v>
       </c>
       <c r="H407" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I407" s="1" t="s">
         <v>10</v>
@@ -12402,7 +12402,7 @@
         <v>39</v>
       </c>
       <c r="H408" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I408" s="1" t="s">
         <v>13</v>
@@ -12434,7 +12434,7 @@
         <v>42</v>
       </c>
       <c r="H409" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I409" s="1" t="s">
         <v>13</v>
@@ -12466,7 +12466,7 @@
         <v>42</v>
       </c>
       <c r="H410" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I410" s="1" t="s">
         <v>10</v>
@@ -12495,7 +12495,7 @@
         <v>62</v>
       </c>
       <c r="H411" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I411" s="1" t="s">
         <v>13</v>
@@ -12527,7 +12527,7 @@
         <v>42</v>
       </c>
       <c r="H412" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I412" s="1" t="s">
         <v>10</v>
@@ -12556,7 +12556,7 @@
         <v>49</v>
       </c>
       <c r="H413" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I413" s="1" t="s">
         <v>10</v>
@@ -12588,7 +12588,7 @@
         <v>42</v>
       </c>
       <c r="H414" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I414" s="1" t="s">
         <v>10</v>
@@ -12620,7 +12620,7 @@
         <v>42</v>
       </c>
       <c r="H415" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I415" s="1" t="s">
         <v>10</v>
@@ -12652,7 +12652,7 @@
         <v>42</v>
       </c>
       <c r="H416" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I416" s="1" t="s">
         <v>10</v>
@@ -12684,7 +12684,7 @@
         <v>42</v>
       </c>
       <c r="H417" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I417" s="1" t="s">
         <v>14</v>
@@ -12708,7 +12708,7 @@
       <c r="J418" s="2"/>
       <c r="K418" s="1"/>
       <c r="M418" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="419" spans="4:13" x14ac:dyDescent="0.3">
@@ -12725,7 +12725,7 @@
         <v>42</v>
       </c>
       <c r="H419" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I419" s="1" t="s">
         <v>13</v>
@@ -12757,7 +12757,7 @@
         <v>42</v>
       </c>
       <c r="H420" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I420" s="1" t="s">
         <v>13</v>
@@ -12789,7 +12789,7 @@
         <v>42</v>
       </c>
       <c r="H421" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I421" s="1" t="s">
         <v>13</v>
@@ -12821,7 +12821,7 @@
         <v>42</v>
       </c>
       <c r="H422" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I422" s="1" t="s">
         <v>10</v>
@@ -12850,7 +12850,7 @@
         <v>37</v>
       </c>
       <c r="H423" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I423" s="1" t="s">
         <v>10</v>
@@ -12879,7 +12879,7 @@
         <v>39</v>
       </c>
       <c r="H424" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I424" s="1" t="s">
         <v>13</v>
@@ -12911,7 +12911,7 @@
         <v>42</v>
       </c>
       <c r="H425" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I425" s="1" t="s">
         <v>10</v>
@@ -12943,7 +12943,7 @@
         <v>42</v>
       </c>
       <c r="H426" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I426" s="1" t="s">
         <v>10</v>
@@ -12972,7 +12972,7 @@
         <v>62</v>
       </c>
       <c r="H427" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I427" s="1" t="s">
         <v>13</v>
@@ -13004,7 +13004,7 @@
         <v>42</v>
       </c>
       <c r="H428" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I428" s="1" t="s">
         <v>10</v>
@@ -13033,7 +13033,7 @@
         <v>49</v>
       </c>
       <c r="H429" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I429" s="1" t="s">
         <v>12</v>
@@ -13057,7 +13057,7 @@
       <c r="J430" s="2"/>
       <c r="K430" s="1"/>
       <c r="M430" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="431" spans="4:13" x14ac:dyDescent="0.3">
@@ -13074,7 +13074,7 @@
         <v>42</v>
       </c>
       <c r="H431" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I431" s="1" t="s">
         <v>10</v>
@@ -13106,7 +13106,7 @@
         <v>42</v>
       </c>
       <c r="H432" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I432" s="1" t="s">
         <v>10</v>
@@ -13138,7 +13138,7 @@
         <v>42</v>
       </c>
       <c r="H433" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I433" s="1" t="s">
         <v>13</v>
@@ -13170,7 +13170,7 @@
         <v>42</v>
       </c>
       <c r="H434" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I434" s="1" t="s">
         <v>13</v>
@@ -13202,7 +13202,7 @@
         <v>42</v>
       </c>
       <c r="H435" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I435" s="1" t="s">
         <v>13</v>
@@ -13234,7 +13234,7 @@
         <v>42</v>
       </c>
       <c r="H436" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I436" s="1" t="s">
         <v>13</v>
@@ -13266,7 +13266,7 @@
         <v>42</v>
       </c>
       <c r="H437" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I437" s="1" t="s">
         <v>13</v>
@@ -13298,7 +13298,7 @@
         <v>42</v>
       </c>
       <c r="H438" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I438" s="1" t="s">
         <v>10</v>
@@ -13327,7 +13327,7 @@
         <v>37</v>
       </c>
       <c r="H439" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I439" s="1" t="s">
         <v>13</v>
@@ -13356,7 +13356,7 @@
         <v>39</v>
       </c>
       <c r="H440" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I440" s="1" t="s">
         <v>13</v>
@@ -13388,7 +13388,7 @@
         <v>42</v>
       </c>
       <c r="H441" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I441" s="1" t="s">
         <v>12</v>
@@ -13412,7 +13412,7 @@
       <c r="J442" s="2"/>
       <c r="K442" s="1"/>
       <c r="M442" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="443" spans="4:13" x14ac:dyDescent="0.3">
@@ -13429,7 +13429,7 @@
         <v>42</v>
       </c>
       <c r="H443" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I443" s="1" t="s">
         <v>13</v>
@@ -13458,7 +13458,7 @@
         <v>62</v>
       </c>
       <c r="H444" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I444" s="1" t="s">
         <v>14</v>
@@ -13482,7 +13482,7 @@
       <c r="J445" s="2"/>
       <c r="K445" s="1"/>
       <c r="M445" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="446" spans="4:13" x14ac:dyDescent="0.3">
@@ -13499,7 +13499,7 @@
         <v>42</v>
       </c>
       <c r="H446" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I446" s="1" t="s">
         <v>10</v>
@@ -13528,7 +13528,7 @@
         <v>49</v>
       </c>
       <c r="H447" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I447" s="1" t="s">
         <v>10</v>
@@ -13560,7 +13560,7 @@
         <v>42</v>
       </c>
       <c r="H448" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I448" s="1" t="s">
         <v>10</v>
@@ -13592,7 +13592,7 @@
         <v>42</v>
       </c>
       <c r="H449" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I449" s="1" t="s">
         <v>10</v>
@@ -13624,7 +13624,7 @@
         <v>42</v>
       </c>
       <c r="H450" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I450" s="1" t="s">
         <v>13</v>
@@ -13656,7 +13656,7 @@
         <v>42</v>
       </c>
       <c r="H451" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I451" s="1" t="s">
         <v>13</v>
@@ -13688,7 +13688,7 @@
         <v>42</v>
       </c>
       <c r="H452" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I452" s="1" t="s">
         <v>10</v>
@@ -13720,7 +13720,7 @@
         <v>42</v>
       </c>
       <c r="H453" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I453" s="1" t="s">
         <v>13</v>
@@ -13752,7 +13752,7 @@
         <v>42</v>
       </c>
       <c r="H454" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I454" s="1" t="s">
         <v>13</v>
@@ -13784,7 +13784,7 @@
         <v>42</v>
       </c>
       <c r="H455" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I455" s="1" t="s">
         <v>10</v>
@@ -13813,7 +13813,7 @@
         <v>37</v>
       </c>
       <c r="H456" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I456" s="1" t="s">
         <v>13</v>
@@ -13842,7 +13842,7 @@
         <v>39</v>
       </c>
       <c r="H457" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I457" s="1" t="s">
         <v>13</v>
@@ -13874,7 +13874,7 @@
         <v>42</v>
       </c>
       <c r="H458" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I458" s="1" t="s">
         <v>13</v>
@@ -13906,7 +13906,7 @@
         <v>42</v>
       </c>
       <c r="H459" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I459" s="1" t="s">
         <v>13</v>
@@ -13935,7 +13935,7 @@
         <v>62</v>
       </c>
       <c r="H460" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I460" s="1" t="s">
         <v>13</v>
@@ -13967,7 +13967,7 @@
         <v>42</v>
       </c>
       <c r="H461" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I461" s="1" t="s">
         <v>10</v>
@@ -13996,7 +13996,7 @@
         <v>49</v>
       </c>
       <c r="H462" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I462" s="1" t="s">
         <v>10</v>
@@ -14028,7 +14028,7 @@
         <v>42</v>
       </c>
       <c r="H463" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I463" s="1" t="s">
         <v>13</v>
@@ -14060,7 +14060,7 @@
         <v>42</v>
       </c>
       <c r="H464" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I464" s="1" t="s">
         <v>10</v>
@@ -14092,7 +14092,7 @@
         <v>42</v>
       </c>
       <c r="H465" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I465" s="1" t="s">
         <v>13</v>
@@ -14124,7 +14124,7 @@
         <v>42</v>
       </c>
       <c r="H466" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I466" s="1" t="s">
         <v>13</v>
@@ -14156,7 +14156,7 @@
         <v>42</v>
       </c>
       <c r="H467" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I467" s="1" t="s">
         <v>13</v>
@@ -14188,7 +14188,7 @@
         <v>42</v>
       </c>
       <c r="H468" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I468" s="1" t="s">
         <v>13</v>
@@ -14220,7 +14220,7 @@
         <v>42</v>
       </c>
       <c r="H469" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I469" s="1" t="s">
         <v>13</v>
@@ -14252,7 +14252,7 @@
         <v>42</v>
       </c>
       <c r="H470" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I470" s="1" t="s">
         <v>10</v>
@@ -14281,7 +14281,7 @@
         <v>37</v>
       </c>
       <c r="H471" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I471" s="1" t="s">
         <v>13</v>
@@ -14310,7 +14310,7 @@
         <v>39</v>
       </c>
       <c r="H472" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I472" s="1" t="s">
         <v>13</v>
@@ -14342,7 +14342,7 @@
         <v>42</v>
       </c>
       <c r="H473" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I473" s="1" t="s">
         <v>13</v>
@@ -14374,7 +14374,7 @@
         <v>42</v>
       </c>
       <c r="H474" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I474" s="1" t="s">
         <v>13</v>
@@ -14403,7 +14403,7 @@
         <v>62</v>
       </c>
       <c r="H475" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I475" s="1" t="s">
         <v>13</v>
@@ -14435,7 +14435,7 @@
         <v>42</v>
       </c>
       <c r="H476" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I476" s="1" t="s">
         <v>10</v>
@@ -14464,7 +14464,7 @@
         <v>49</v>
       </c>
       <c r="H477" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I477" s="1" t="s">
         <v>10</v>
@@ -14496,7 +14496,7 @@
         <v>42</v>
       </c>
       <c r="H478" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I478" s="1" t="s">
         <v>13</v>
@@ -14528,7 +14528,7 @@
         <v>42</v>
       </c>
       <c r="H479" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I479" s="1" t="s">
         <v>13</v>
@@ -14560,7 +14560,7 @@
         <v>42</v>
       </c>
       <c r="H480" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I480" s="1" t="s">
         <v>10</v>
@@ -14592,7 +14592,7 @@
         <v>42</v>
       </c>
       <c r="H481" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I481" s="1" t="s">
         <v>14</v>
@@ -14616,7 +14616,7 @@
       <c r="J482" s="2"/>
       <c r="K482" s="1"/>
       <c r="M482" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="483" spans="4:13" x14ac:dyDescent="0.3">
@@ -14633,7 +14633,7 @@
         <v>42</v>
       </c>
       <c r="H483" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I483" s="1" t="s">
         <v>13</v>
@@ -14665,7 +14665,7 @@
         <v>42</v>
       </c>
       <c r="H484" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I484" s="1" t="s">
         <v>13</v>
@@ -14697,7 +14697,7 @@
         <v>42</v>
       </c>
       <c r="H485" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I485" s="1" t="s">
         <v>13</v>
@@ -14729,7 +14729,7 @@
         <v>42</v>
       </c>
       <c r="H486" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I486" s="1" t="s">
         <v>10</v>
@@ -14758,7 +14758,7 @@
         <v>37</v>
       </c>
       <c r="H487" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I487" s="1" t="s">
         <v>13</v>
@@ -14787,7 +14787,7 @@
         <v>39</v>
       </c>
       <c r="H488" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I488" s="1" t="s">
         <v>13</v>
@@ -14819,7 +14819,7 @@
         <v>42</v>
       </c>
       <c r="H489" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I489" s="1" t="s">
         <v>13</v>
@@ -14851,7 +14851,7 @@
         <v>42</v>
       </c>
       <c r="H490" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I490" s="1" t="s">
         <v>10</v>
@@ -14880,7 +14880,7 @@
         <v>62</v>
       </c>
       <c r="H491" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I491" s="1" t="s">
         <v>13</v>
@@ -14912,7 +14912,7 @@
         <v>42</v>
       </c>
       <c r="H492" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I492" s="1" t="s">
         <v>10</v>
@@ -14941,7 +14941,7 @@
         <v>49</v>
       </c>
       <c r="H493" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I493" s="1" t="s">
         <v>12</v>
@@ -14965,7 +14965,7 @@
       <c r="J494" s="2"/>
       <c r="K494" s="1"/>
       <c r="M494" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="495" spans="4:13" x14ac:dyDescent="0.3">
@@ -14982,7 +14982,7 @@
         <v>42</v>
       </c>
       <c r="H495" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I495" s="1" t="s">
         <v>10</v>
@@ -15014,7 +15014,7 @@
         <v>42</v>
       </c>
       <c r="H496" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I496" s="1" t="s">
         <v>12</v>
@@ -15038,7 +15038,7 @@
       <c r="J497" s="2"/>
       <c r="K497" s="1"/>
       <c r="M497" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="498" spans="4:13" x14ac:dyDescent="0.3">
@@ -15055,7 +15055,7 @@
         <v>42</v>
       </c>
       <c r="H498" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I498" s="1" t="s">
         <v>10</v>
@@ -15087,7 +15087,7 @@
         <v>42</v>
       </c>
       <c r="H499" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I499" s="1" t="s">
         <v>10</v>
@@ -15119,7 +15119,7 @@
         <v>42</v>
       </c>
       <c r="H500" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I500" s="1" t="s">
         <v>13</v>
@@ -15151,7 +15151,7 @@
         <v>42</v>
       </c>
       <c r="H501" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I501" s="1" t="s">
         <v>13</v>
@@ -15183,7 +15183,7 @@
         <v>42</v>
       </c>
       <c r="H502" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I502" s="1" t="s">
         <v>13</v>
@@ -15215,7 +15215,7 @@
         <v>42</v>
       </c>
       <c r="H503" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I503" s="1" t="s">
         <v>10</v>
@@ -15247,7 +15247,7 @@
         <v>42</v>
       </c>
       <c r="H504" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I504" s="1" t="s">
         <v>10</v>
@@ -15279,7 +15279,7 @@
         <v>42</v>
       </c>
       <c r="H505" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I505" s="1" t="s">
         <v>10</v>
@@ -15311,7 +15311,7 @@
         <v>42</v>
       </c>
       <c r="H506" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I506" s="1" t="s">
         <v>10</v>
@@ -15343,7 +15343,7 @@
         <v>42</v>
       </c>
       <c r="H507" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I507" s="1" t="s">
         <v>10</v>
@@ -15375,7 +15375,7 @@
         <v>42</v>
       </c>
       <c r="H508" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I508" s="1" t="s">
         <v>10</v>
@@ -15465,7 +15465,7 @@
         <v>37</v>
       </c>
       <c r="H511" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I511" s="1" t="s">
         <v>13</v>
@@ -15494,7 +15494,7 @@
         <v>39</v>
       </c>
       <c r="H512" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I512" s="1" t="s">
         <v>13</v>
@@ -15526,7 +15526,7 @@
         <v>42</v>
       </c>
       <c r="H513" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I513" s="1" t="s">
         <v>13</v>
@@ -15558,7 +15558,7 @@
         <v>42</v>
       </c>
       <c r="H514" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I514" s="1" t="s">
         <v>10</v>
@@ -15587,7 +15587,7 @@
         <v>62</v>
       </c>
       <c r="H515" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I515" s="1" t="s">
         <v>13</v>
@@ -15619,7 +15619,7 @@
         <v>42</v>
       </c>
       <c r="H516" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I516" s="1" t="s">
         <v>10</v>
@@ -15651,7 +15651,7 @@
         <v>42</v>
       </c>
       <c r="H517" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I517" s="1" t="s">
         <v>10</v>
@@ -15683,7 +15683,7 @@
         <v>42</v>
       </c>
       <c r="H518" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I518" s="1" t="s">
         <v>10</v>
@@ -15715,7 +15715,7 @@
         <v>42</v>
       </c>
       <c r="H519" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I519" s="1" t="s">
         <v>10</v>
@@ -15747,7 +15747,7 @@
         <v>42</v>
       </c>
       <c r="H520" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I520" s="1" t="s">
         <v>13</v>
@@ -15798,138 +15798,470 @@
       </c>
     </row>
     <row r="522" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H522" s="2"/>
-      <c r="I522" s="1"/>
-      <c r="J522" s="2"/>
-      <c r="K522" s="1"/>
+      <c r="D522" t="s">
+        <v>36</v>
+      </c>
+      <c r="E522">
+        <v>1926</v>
+      </c>
+      <c r="F522" t="s">
+        <v>37</v>
+      </c>
+      <c r="H522" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I522" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J522" s="2">
+        <v>5.4629629629629632E-2</v>
+      </c>
+      <c r="K522" s="1">
+        <v>46219.62939814815</v>
+      </c>
+      <c r="L522">
+        <v>0</v>
+      </c>
+      <c r="M522" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="523" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H523" s="2"/>
-      <c r="I523" s="1"/>
-      <c r="J523" s="2"/>
-      <c r="K523" s="1"/>
+      <c r="D523" t="s">
+        <v>36</v>
+      </c>
+      <c r="E523">
+        <v>3789</v>
+      </c>
+      <c r="F523" t="s">
+        <v>63</v>
+      </c>
+      <c r="G523" t="s">
+        <v>42</v>
+      </c>
+      <c r="H523" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I523" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J523" s="2">
+        <v>0</v>
+      </c>
+      <c r="K523" s="1">
+        <v>46219.62939814815</v>
+      </c>
+      <c r="L523">
+        <v>0</v>
+      </c>
+      <c r="M523" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="524" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H524" s="2"/>
-      <c r="I524" s="1"/>
-      <c r="J524" s="2"/>
-      <c r="K524" s="1"/>
+      <c r="D524" t="s">
+        <v>36</v>
+      </c>
+      <c r="E524">
+        <v>1932</v>
+      </c>
+      <c r="F524" t="s">
+        <v>45</v>
+      </c>
+      <c r="G524" t="s">
+        <v>42</v>
+      </c>
+      <c r="H524" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I524" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J524" s="2">
+        <v>0</v>
+      </c>
+      <c r="K524" s="1">
+        <v>46219.63009259259</v>
+      </c>
+      <c r="L524">
+        <v>0</v>
+      </c>
+      <c r="M524" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="525" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H525" s="2"/>
-      <c r="I525" s="1"/>
-      <c r="J525" s="2"/>
-      <c r="K525" s="1"/>
+      <c r="D525" t="s">
+        <v>36</v>
+      </c>
+      <c r="E525">
+        <v>1935</v>
+      </c>
+      <c r="F525" t="s">
+        <v>48</v>
+      </c>
+      <c r="G525" t="s">
+        <v>42</v>
+      </c>
+      <c r="H525" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I525" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J525" s="2">
+        <v>0</v>
+      </c>
+      <c r="K525" s="1">
+        <v>46219.630787037036</v>
+      </c>
+      <c r="L525">
+        <v>0</v>
+      </c>
+      <c r="M525" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="526" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H526" s="2"/>
-      <c r="I526" s="1"/>
-      <c r="J526" s="2"/>
-      <c r="K526" s="1"/>
+      <c r="D526" t="s">
+        <v>36</v>
+      </c>
+      <c r="E526">
+        <v>1936</v>
+      </c>
+      <c r="F526" t="s">
+        <v>49</v>
+      </c>
+      <c r="H526" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I526" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J526" s="2">
+        <v>0</v>
+      </c>
+      <c r="K526" s="1">
+        <v>46219.630787037036</v>
+      </c>
+      <c r="L526">
+        <v>0</v>
+      </c>
+      <c r="M526" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="527" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H527" s="2"/>
-      <c r="I527" s="1"/>
-      <c r="J527" s="2"/>
-      <c r="K527" s="1"/>
+      <c r="D527" t="s">
+        <v>36</v>
+      </c>
+      <c r="E527">
+        <v>3890</v>
+      </c>
+      <c r="F527" t="s">
+        <v>65</v>
+      </c>
+      <c r="G527" t="s">
+        <v>42</v>
+      </c>
+      <c r="H527" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I527" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J527" s="2">
+        <v>0</v>
+      </c>
+      <c r="K527" s="1">
+        <v>46219.631481481483</v>
+      </c>
+      <c r="L527">
+        <v>0</v>
+      </c>
+      <c r="M527" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="528" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H528" s="2"/>
-      <c r="I528" s="1"/>
-      <c r="J528" s="2"/>
-      <c r="K528" s="1"/>
-    </row>
-    <row r="529" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H529" s="2"/>
-      <c r="I529" s="1"/>
-      <c r="J529" s="2"/>
-      <c r="K529" s="1"/>
-    </row>
-    <row r="530" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H530" s="2"/>
-      <c r="I530" s="1"/>
-      <c r="J530" s="2"/>
-      <c r="K530" s="1"/>
-    </row>
-    <row r="531" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H531" s="2"/>
-      <c r="I531" s="1"/>
-      <c r="J531" s="2"/>
-      <c r="K531" s="1"/>
-    </row>
-    <row r="532" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H532" s="2"/>
-      <c r="I532" s="1"/>
-      <c r="J532" s="2"/>
-      <c r="K532" s="1"/>
-    </row>
-    <row r="533" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H533" s="2"/>
-      <c r="I533" s="1"/>
-      <c r="J533" s="2"/>
-      <c r="K533" s="1"/>
-    </row>
-    <row r="534" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H534" s="2"/>
-      <c r="I534" s="1"/>
-      <c r="J534" s="2"/>
-      <c r="K534" s="1"/>
-    </row>
-    <row r="535" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D528" t="s">
+        <v>36</v>
+      </c>
+      <c r="E528">
+        <v>1937</v>
+      </c>
+      <c r="F528" t="s">
+        <v>50</v>
+      </c>
+      <c r="G528" t="s">
+        <v>42</v>
+      </c>
+      <c r="H528" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I528" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J528" s="2">
+        <v>8.3796296296296292E-3</v>
+      </c>
+      <c r="K528" s="1">
+        <v>46219.632175925923</v>
+      </c>
+      <c r="L528">
+        <v>0</v>
+      </c>
+      <c r="M528" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="529" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D529" t="s">
+        <v>36</v>
+      </c>
+      <c r="E529">
+        <v>3788</v>
+      </c>
+      <c r="F529" t="s">
+        <v>64</v>
+      </c>
+      <c r="G529" t="s">
+        <v>42</v>
+      </c>
+      <c r="H529" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I529" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J529" s="2">
+        <v>0</v>
+      </c>
+      <c r="K529" s="1">
+        <v>46219.632870370369</v>
+      </c>
+      <c r="L529">
+        <v>0</v>
+      </c>
+      <c r="M529" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="530" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D530" t="s">
+        <v>36</v>
+      </c>
+      <c r="E530">
+        <v>3868</v>
+      </c>
+      <c r="F530" t="s">
+        <v>42</v>
+      </c>
+      <c r="G530" t="s">
+        <v>42</v>
+      </c>
+      <c r="H530" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I530" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J530" s="2">
+        <v>0</v>
+      </c>
+      <c r="K530" s="1">
+        <v>46219.633564814816</v>
+      </c>
+      <c r="L530">
+        <v>0</v>
+      </c>
+      <c r="M530" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="531" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D531" t="s">
+        <v>36</v>
+      </c>
+      <c r="E531">
+        <v>1939</v>
+      </c>
+      <c r="F531" t="s">
+        <v>52</v>
+      </c>
+      <c r="G531" t="s">
+        <v>42</v>
+      </c>
+      <c r="H531" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I531" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J531" s="2">
+        <v>0</v>
+      </c>
+      <c r="K531" s="1">
+        <v>46219.633564814816</v>
+      </c>
+      <c r="L531">
+        <v>0</v>
+      </c>
+      <c r="M531" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="532" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D532" t="s">
+        <v>36</v>
+      </c>
+      <c r="E532">
+        <v>1941</v>
+      </c>
+      <c r="F532" t="s">
+        <v>54</v>
+      </c>
+      <c r="G532" t="s">
+        <v>42</v>
+      </c>
+      <c r="H532" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I532" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J532" s="2">
+        <v>0</v>
+      </c>
+      <c r="K532" s="1">
+        <v>46219.634259259263</v>
+      </c>
+      <c r="L532">
+        <v>0</v>
+      </c>
+      <c r="M532" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="533" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D533" t="s">
+        <v>36</v>
+      </c>
+      <c r="E533">
+        <v>1942</v>
+      </c>
+      <c r="F533" t="s">
+        <v>55</v>
+      </c>
+      <c r="G533" t="s">
+        <v>42</v>
+      </c>
+      <c r="H533" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I533" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J533" s="2">
+        <v>0</v>
+      </c>
+      <c r="K533" s="1">
+        <v>46219.634953703702</v>
+      </c>
+      <c r="L533">
+        <v>0</v>
+      </c>
+      <c r="M533" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="534" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D534" t="s">
+        <v>36</v>
+      </c>
+      <c r="E534">
+        <v>1944</v>
+      </c>
+      <c r="F534" t="s">
+        <v>57</v>
+      </c>
+      <c r="G534" t="s">
+        <v>42</v>
+      </c>
+      <c r="H534" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I534" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J534" s="2">
+        <v>6.076388888888889E-3</v>
+      </c>
+      <c r="K534" s="1">
+        <v>46219.634953703702</v>
+      </c>
+      <c r="L534">
+        <v>0</v>
+      </c>
+      <c r="M534" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="535" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H535" s="2"/>
       <c r="I535" s="1"/>
       <c r="J535" s="2"/>
       <c r="K535" s="1"/>
     </row>
-    <row r="536" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="536" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H536" s="2"/>
       <c r="I536" s="1"/>
       <c r="J536" s="2"/>
       <c r="K536" s="1"/>
     </row>
-    <row r="537" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="537" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H537" s="2"/>
       <c r="I537" s="1"/>
       <c r="J537" s="2"/>
       <c r="K537" s="1"/>
     </row>
-    <row r="538" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="538" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H538" s="2"/>
       <c r="I538" s="1"/>
       <c r="J538" s="2"/>
       <c r="K538" s="1"/>
     </row>
-    <row r="539" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="539" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H539" s="2"/>
       <c r="I539" s="1"/>
       <c r="J539" s="2"/>
       <c r="K539" s="1"/>
     </row>
-    <row r="540" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="540" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H540" s="2"/>
       <c r="I540" s="1"/>
       <c r="J540" s="2"/>
       <c r="K540" s="1"/>
     </row>
-    <row r="541" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="541" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H541" s="2"/>
       <c r="I541" s="1"/>
       <c r="J541" s="2"/>
       <c r="K541" s="1"/>
     </row>
-    <row r="542" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="542" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H542" s="2"/>
       <c r="I542" s="1"/>
       <c r="J542" s="2"/>
       <c r="K542" s="1"/>
     </row>
-    <row r="543" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="543" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H543" s="2"/>
       <c r="I543" s="1"/>
       <c r="J543" s="2"/>
       <c r="K543" s="1"/>
     </row>
-    <row r="544" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="544" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H544" s="2"/>
       <c r="I544" s="1"/>
       <c r="J544" s="2"/>
@@ -17356,6 +17688,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -17385,6 +17718,7 @@
     <row r="787" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H787" s="2"/>
       <c r="I787" s="1"/>
+      <c r="J787" s="2"/>
       <c r="K787" s="1"/>
     </row>
     <row r="788" spans="8:11" x14ac:dyDescent="0.3">
@@ -17450,6 +17784,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -17473,6 +17808,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -17490,6 +17826,7 @@
     <row r="805" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H805" s="2"/>
       <c r="I805" s="1"/>
+      <c r="J805" s="2"/>
       <c r="K805" s="1"/>
     </row>
     <row r="806" spans="8:11" x14ac:dyDescent="0.3">
@@ -17507,6 +17844,7 @@
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H808" s="2"/>
       <c r="I808" s="1"/>
+      <c r="J808" s="2"/>
       <c r="K808" s="1"/>
     </row>
     <row r="809" spans="8:11" x14ac:dyDescent="0.3">
@@ -17626,6 +17964,7 @@
     <row r="828" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H828" s="2"/>
       <c r="I828" s="1"/>
+      <c r="J828" s="2"/>
       <c r="K828" s="1"/>
     </row>
     <row r="829" spans="8:11" x14ac:dyDescent="0.3">
@@ -17709,6 +18048,7 @@
     <row r="842" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H842" s="2"/>
       <c r="I842" s="1"/>
+      <c r="J842" s="2"/>
       <c r="K842" s="1"/>
     </row>
     <row r="843" spans="8:11" x14ac:dyDescent="0.3">
@@ -17732,6 +18072,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -17743,6 +18084,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -17754,6 +18096,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -17801,6 +18144,7 @@
     <row r="858" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H858" s="2"/>
       <c r="I858" s="1"/>
+      <c r="J858" s="2"/>
       <c r="K858" s="1"/>
     </row>
     <row r="859" spans="8:11" x14ac:dyDescent="0.3">
@@ -17854,6 +18198,7 @@
     <row r="867" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
+      <c r="J867" s="2"/>
       <c r="K867" s="1"/>
     </row>
     <row r="868" spans="8:11" x14ac:dyDescent="0.3">
@@ -18026,6 +18371,7 @@
     <row r="896" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H896" s="2"/>
       <c r="I896" s="1"/>
+      <c r="J896" s="2"/>
       <c r="K896" s="1"/>
     </row>
     <row r="897" spans="8:11" x14ac:dyDescent="0.3">
@@ -18037,6 +18383,7 @@
     <row r="898" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H898" s="2"/>
       <c r="I898" s="1"/>
+      <c r="J898" s="2"/>
       <c r="K898" s="1"/>
     </row>
     <row r="899" spans="8:11" x14ac:dyDescent="0.3">
@@ -18114,6 +18461,7 @@
     <row r="911" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
+      <c r="J911" s="2"/>
       <c r="K911" s="1"/>
     </row>
     <row r="912" spans="8:11" x14ac:dyDescent="0.3">
@@ -18131,6 +18479,7 @@
     <row r="914" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H914" s="2"/>
       <c r="I914" s="1"/>
+      <c r="J914" s="2"/>
       <c r="K914" s="1"/>
     </row>
     <row r="915" spans="8:11" x14ac:dyDescent="0.3">
@@ -18178,6 +18527,7 @@
     <row r="922" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H922" s="2"/>
       <c r="I922" s="1"/>
+      <c r="J922" s="2"/>
       <c r="K922" s="1"/>
     </row>
     <row r="923" spans="8:11" x14ac:dyDescent="0.3">
@@ -18290,6 +18640,7 @@
     <row r="941" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H941" s="2"/>
       <c r="I941" s="1"/>
+      <c r="J941" s="2"/>
       <c r="K941" s="1"/>
     </row>
     <row r="942" spans="8:11" x14ac:dyDescent="0.3">
@@ -18349,6 +18700,7 @@
     <row r="951" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H951" s="2"/>
       <c r="I951" s="1"/>
+      <c r="J951" s="2"/>
       <c r="K951" s="1"/>
     </row>
     <row r="952" spans="8:11" x14ac:dyDescent="0.3">
@@ -18360,6 +18712,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -18431,6 +18784,7 @@
     <row r="965" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H965" s="2"/>
       <c r="I965" s="1"/>
+      <c r="J965" s="2"/>
       <c r="K965" s="1"/>
     </row>
     <row r="966" spans="8:11" x14ac:dyDescent="0.3">
@@ -18483,6 +18837,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -18559,11 +18914,13 @@
     <row r="987" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H987" s="2"/>
       <c r="I987" s="1"/>
+      <c r="J987" s="2"/>
       <c r="K987" s="1"/>
     </row>
     <row r="988" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H988" s="2"/>
       <c r="I988" s="1"/>
+      <c r="J988" s="2"/>
       <c r="K988" s="1"/>
     </row>
     <row r="989" spans="8:11" x14ac:dyDescent="0.3">
@@ -18623,6 +18980,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -18634,6 +18992,7 @@
     <row r="1000" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
+      <c r="J1000" s="2"/>
       <c r="K1000" s="1"/>
     </row>
     <row r="1001" spans="8:11" x14ac:dyDescent="0.3">
@@ -18645,11 +19004,13 @@
     <row r="1002" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
+      <c r="J1002" s="2"/>
       <c r="K1002" s="1"/>
     </row>
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -18703,6 +19064,7 @@
     <row r="1012" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1012" s="2"/>
       <c r="I1012" s="1"/>
+      <c r="J1012" s="2"/>
       <c r="K1012" s="1"/>
     </row>
     <row r="1013" spans="8:11" x14ac:dyDescent="0.3">
@@ -18719,6 +19081,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -18742,6 +19105,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -18759,6 +19123,7 @@
     <row r="1022" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1022" s="2"/>
       <c r="I1022" s="1"/>
+      <c r="J1022" s="2"/>
       <c r="K1022" s="1"/>
     </row>
     <row r="1023" spans="8:11" x14ac:dyDescent="0.3">
@@ -18805,11 +19170,13 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1031" s="2"/>
       <c r="I1031" s="1"/>
+      <c r="J1031" s="2"/>
       <c r="K1031" s="1"/>
     </row>
     <row r="1032" spans="8:11" x14ac:dyDescent="0.3">
@@ -18851,11 +19218,13 @@
     <row r="1038" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1038" s="2"/>
       <c r="I1038" s="1"/>
+      <c r="J1038" s="2"/>
       <c r="K1038" s="1"/>
     </row>
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -18873,6 +19242,7 @@
     <row r="1042" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1042" s="2"/>
       <c r="I1042" s="1"/>
+      <c r="J1042" s="2"/>
       <c r="K1042" s="1"/>
     </row>
     <row r="1043" spans="8:11" x14ac:dyDescent="0.3">
@@ -18884,6 +19254,7 @@
     <row r="1044" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1044" s="2"/>
       <c r="I1044" s="1"/>
+      <c r="J1044" s="2"/>
       <c r="K1044" s="1"/>
     </row>
     <row r="1045" spans="8:11" x14ac:dyDescent="0.3">
@@ -18895,6 +19266,7 @@
     <row r="1046" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1046" s="2"/>
       <c r="I1046" s="1"/>
+      <c r="J1046" s="2"/>
       <c r="K1046" s="1"/>
     </row>
     <row r="1047" spans="8:11" x14ac:dyDescent="0.3">
@@ -18912,6 +19284,7 @@
     <row r="1049" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1049" s="2"/>
       <c r="I1049" s="1"/>
+      <c r="J1049" s="2"/>
       <c r="K1049" s="1"/>
     </row>
     <row r="1050" spans="8:11" x14ac:dyDescent="0.3">
@@ -18989,6 +19362,7 @@
     <row r="1062" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1062" s="2"/>
       <c r="I1062" s="1"/>
+      <c r="J1062" s="2"/>
       <c r="K1062" s="1"/>
     </row>
     <row r="1063" spans="8:11" x14ac:dyDescent="0.3">
@@ -19018,6 +19392,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -19029,16 +19404,19 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1070" s="2"/>
       <c r="I1070" s="1"/>
+      <c r="J1070" s="2"/>
       <c r="K1070" s="1"/>
     </row>
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -19050,16 +19428,19 @@
     <row r="1073" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1073" s="2"/>
       <c r="I1073" s="1"/>
+      <c r="J1073" s="2"/>
       <c r="K1073" s="1"/>
     </row>
     <row r="1074" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1074" s="2"/>
       <c r="I1074" s="1"/>
+      <c r="J1074" s="2"/>
       <c r="K1074" s="1"/>
     </row>
     <row r="1075" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1075" s="2"/>
       <c r="I1075" s="1"/>
+      <c r="J1075" s="2"/>
       <c r="K1075" s="1"/>
     </row>
     <row r="1076" spans="8:11" x14ac:dyDescent="0.3">
@@ -19071,11 +19452,13 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1078" s="2"/>
       <c r="I1078" s="1"/>
+      <c r="J1078" s="2"/>
       <c r="K1078" s="1"/>
     </row>
     <row r="1079" spans="8:11" x14ac:dyDescent="0.3">
@@ -19099,6 +19482,7 @@
     <row r="1082" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1082" s="2"/>
       <c r="I1082" s="1"/>
+      <c r="J1082" s="2"/>
       <c r="K1082" s="1"/>
     </row>
     <row r="1083" spans="8:11" x14ac:dyDescent="0.3">
@@ -19140,6 +19524,7 @@
     <row r="1089" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1089" s="2"/>
       <c r="I1089" s="1"/>
+      <c r="J1089" s="2"/>
       <c r="K1089" s="1"/>
     </row>
     <row r="1090" spans="8:11" x14ac:dyDescent="0.3">
@@ -19169,21 +19554,25 @@
     <row r="1094" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1094" s="2"/>
       <c r="I1094" s="1"/>
+      <c r="J1094" s="2"/>
       <c r="K1094" s="1"/>
     </row>
     <row r="1095" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1095" s="2"/>
       <c r="I1095" s="1"/>
+      <c r="J1095" s="2"/>
       <c r="K1095" s="1"/>
     </row>
     <row r="1096" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1096" s="2"/>
       <c r="I1096" s="1"/>
+      <c r="J1096" s="2"/>
       <c r="K1096" s="1"/>
     </row>
     <row r="1097" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1097" s="2"/>
       <c r="I1097" s="1"/>
+      <c r="J1097" s="2"/>
       <c r="K1097" s="1"/>
     </row>
     <row r="1098" spans="8:11" x14ac:dyDescent="0.3">
@@ -19195,6 +19584,7 @@
     <row r="1099" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
+      <c r="J1099" s="2"/>
       <c r="K1099" s="1"/>
     </row>
     <row r="1100" spans="8:11" x14ac:dyDescent="0.3">
@@ -19212,6 +19602,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -19251,11 +19642,13 @@
     <row r="1109" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1109" s="2"/>
       <c r="I1109" s="1"/>
+      <c r="J1109" s="2"/>
       <c r="K1109" s="1"/>
     </row>
     <row r="1110" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1110" s="2"/>
       <c r="I1110" s="1"/>
+      <c r="J1110" s="2"/>
       <c r="K1110" s="1"/>
     </row>
     <row r="1111" spans="8:11" x14ac:dyDescent="0.3">
@@ -19303,6 +19696,7 @@
     <row r="1118" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
+      <c r="J1118" s="2"/>
       <c r="K1118" s="1"/>
     </row>
     <row r="1119" spans="8:11" x14ac:dyDescent="0.3">
@@ -19332,6 +19726,7 @@
     <row r="1123" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1123" s="2"/>
       <c r="I1123" s="1"/>
+      <c r="J1123" s="2"/>
       <c r="K1123" s="1"/>
     </row>
     <row r="1124" spans="8:11" x14ac:dyDescent="0.3">
@@ -19408,6 +19803,7 @@
     <row r="1136" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1136" s="2"/>
       <c r="I1136" s="1"/>
+      <c r="J1136" s="2"/>
       <c r="K1136" s="1"/>
     </row>
     <row r="1137" spans="8:11" x14ac:dyDescent="0.3">
@@ -19454,6 +19850,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -19489,11 +19886,13 @@
     <row r="1150" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1150" s="2"/>
       <c r="I1150" s="1"/>
+      <c r="J1150" s="2"/>
       <c r="K1150" s="1"/>
     </row>
     <row r="1151" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
+      <c r="J1151" s="2"/>
       <c r="K1151" s="1"/>
     </row>
     <row r="1152" spans="8:11" x14ac:dyDescent="0.3">
@@ -19510,6 +19909,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -19520,6 +19920,7 @@
     <row r="1156" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1156" s="2"/>
       <c r="I1156" s="1"/>
+      <c r="J1156" s="2"/>
       <c r="K1156" s="1"/>
     </row>
     <row r="1157" spans="8:11" x14ac:dyDescent="0.3">
@@ -19555,6 +19956,7 @@
     <row r="1162" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1162" s="2"/>
       <c r="I1162" s="1"/>
+      <c r="J1162" s="2"/>
       <c r="K1162" s="1"/>
     </row>
     <row r="1163" spans="8:11" x14ac:dyDescent="0.3">
@@ -19566,6 +19968,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -19577,6 +19980,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -19588,6 +19992,7 @@
     <row r="1168" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1168" s="2"/>
       <c r="I1168" s="1"/>
+      <c r="J1168" s="2"/>
       <c r="K1168" s="1"/>
     </row>
     <row r="1169" spans="8:11" x14ac:dyDescent="0.3">
@@ -19599,6 +20004,7 @@
     <row r="1170" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
+      <c r="J1170" s="2"/>
       <c r="K1170" s="1"/>
     </row>
     <row r="1171" spans="8:11" x14ac:dyDescent="0.3">
@@ -19640,6 +20046,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -19657,6 +20064,7 @@
     <row r="1180" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1180" s="2"/>
       <c r="I1180" s="1"/>
+      <c r="J1180" s="2"/>
       <c r="K1180" s="1"/>
     </row>
     <row r="1181" spans="8:11" x14ac:dyDescent="0.3">
@@ -19674,6 +20082,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -19715,6 +20124,7 @@
     <row r="1190" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1190" s="2"/>
       <c r="I1190" s="1"/>
+      <c r="J1190" s="2"/>
       <c r="K1190" s="1"/>
     </row>
     <row r="1191" spans="8:11" x14ac:dyDescent="0.3">
@@ -19738,6 +20148,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -19784,6 +20195,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -19819,6 +20231,7 @@
     <row r="1208" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1208" s="2"/>
       <c r="I1208" s="1"/>
+      <c r="J1208" s="2"/>
       <c r="K1208" s="1"/>
     </row>
     <row r="1209" spans="8:11" x14ac:dyDescent="0.3">
@@ -19842,6 +20255,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -19882,6 +20296,7 @@
     <row r="1219" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1219" s="2"/>
       <c r="I1219" s="1"/>
+      <c r="J1219" s="2"/>
       <c r="K1219" s="1"/>
     </row>
     <row r="1220" spans="8:11" x14ac:dyDescent="0.3">
@@ -19899,11 +20314,13 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1223" s="2"/>
       <c r="I1223" s="1"/>
+      <c r="J1223" s="2"/>
       <c r="K1223" s="1"/>
     </row>
     <row r="1224" spans="8:11" x14ac:dyDescent="0.3">
@@ -19962,6 +20379,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -19978,6 +20396,7 @@
     <row r="1236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1236" s="2"/>
       <c r="I1236" s="1"/>
+      <c r="J1236" s="2"/>
       <c r="K1236" s="1"/>
     </row>
     <row r="1237" spans="8:11" x14ac:dyDescent="0.3">
@@ -19989,6 +20408,7 @@
     <row r="1238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1238" s="2"/>
       <c r="I1238" s="1"/>
+      <c r="J1238" s="2"/>
       <c r="K1238" s="1"/>
     </row>
     <row r="1239" spans="8:11" x14ac:dyDescent="0.3">
@@ -20000,11 +20420,13 @@
     <row r="1240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1240" s="2"/>
       <c r="I1240" s="1"/>
+      <c r="J1240" s="2"/>
       <c r="K1240" s="1"/>
     </row>
     <row r="1241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1241" s="2"/>
       <c r="I1241" s="1"/>
+      <c r="J1241" s="2"/>
       <c r="K1241" s="1"/>
     </row>
     <row r="1242" spans="8:11" x14ac:dyDescent="0.3">
@@ -20040,6 +20462,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -20092,6 +20515,7 @@
     <row r="1256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
+      <c r="J1256" s="2"/>
       <c r="K1256" s="1"/>
     </row>
     <row r="1257" spans="8:11" x14ac:dyDescent="0.3">
@@ -20102,6 +20526,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -20117,6 +20542,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -20140,16 +20566,19 @@
     <row r="1265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1265" s="2"/>
       <c r="I1265" s="1"/>
+      <c r="J1265" s="2"/>
       <c r="K1265" s="1"/>
     </row>
     <row r="1266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1266" s="2"/>
       <c r="I1266" s="1"/>
+      <c r="J1266" s="2"/>
       <c r="K1266" s="1"/>
     </row>
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -20220,6 +20649,7 @@
     <row r="1279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
+      <c r="J1279" s="2"/>
       <c r="K1279" s="1"/>
     </row>
     <row r="1280" spans="8:11" x14ac:dyDescent="0.3">
@@ -20231,6 +20661,7 @@
     <row r="1281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1281" s="2"/>
       <c r="I1281" s="1"/>
+      <c r="J1281" s="2"/>
       <c r="K1281" s="1"/>
     </row>
     <row r="1282" spans="8:11" x14ac:dyDescent="0.3">
@@ -20331,6 +20762,8 @@
     <row r="1298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1298" s="2"/>
       <c r="I1298" s="1"/>
+      <c r="J1298" s="2"/>
+      <c r="K1298" s="1"/>
     </row>
     <row r="1299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1299" s="2"/>
@@ -20387,6 +20820,7 @@
     <row r="1308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1308" s="2"/>
       <c r="I1308" s="1"/>
+      <c r="J1308" s="2"/>
       <c r="K1308" s="1"/>
     </row>
     <row r="1309" spans="8:11" x14ac:dyDescent="0.3">
@@ -20410,6 +20844,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -20534,6 +20969,7 @@
     <row r="1333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1333" s="2"/>
       <c r="I1333" s="1"/>
+      <c r="J1333" s="2"/>
       <c r="K1333" s="1"/>
     </row>
     <row r="1334" spans="8:11" x14ac:dyDescent="0.3">
@@ -20692,6 +21128,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -20709,6 +21146,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -20749,6 +21187,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -21081,6 +21520,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -21169,6 +21609,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -21262,6 +21703,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -21321,11 +21763,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -21377,6 +21821,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -21418,6 +21863,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -21462,6 +21908,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -21508,11 +21955,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -21710,6 +22159,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -21739,6 +22189,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -21754,6 +22206,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -21813,6 +22266,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -21884,6 +22338,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -21925,6 +22380,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -22043,6 +22499,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -22107,6 +22564,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -22231,6 +22689,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -22457,6 +22916,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -22574,6 +23034,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -22657,6 +23118,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -22716,6 +23178,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -22739,6 +23202,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -22786,6 +23250,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -22845,6 +23310,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -22868,6 +23334,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -22885,6 +23352,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -22968,6 +23436,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -23159,6 +23628,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -51015,6 +51485,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -51022,6 +51493,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -51029,6 +51501,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -51044,6 +51517,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -51053,6 +51527,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -51060,9 +51535,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -51070,12 +51551,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -51083,12 +51567,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -51100,9 +51587,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -51117,6 +51606,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -51143,6 +51633,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -51153,7 +51644,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -51161,6 +51657,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -51172,6 +51669,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -51179,6 +51677,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -51193,13 +51692,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -51210,15 +51715,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -51234,6 +51742,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -51252,6 +51761,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -51263,6 +51773,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -51280,18 +51791,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -51320,6 +51836,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -51327,9 +51844,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -51352,12 +51871,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -51372,9 +51894,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -51390,12 +51914,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -51416,6 +51942,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -51427,9 +51954,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -51441,6 +51970,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -51480,9 +52010,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -51490,9 +52022,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -51503,6 +52037,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -51510,18 +52045,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -51529,6 +52072,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -51539,6 +52083,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -51565,15 +52110,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -51595,6 +52144,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -51602,9 +52152,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -51612,6 +52164,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -51623,6 +52176,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -51637,6 +52191,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -51646,6 +52204,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -51657,6 +52216,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -51667,10 +52227,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -51678,6 +52243,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -51692,6 +52258,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -51714,6 +52281,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -51733,25 +52301,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -51759,6 +52339,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -51766,15 +52347,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -51788,6 +52376,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -51806,9 +52395,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -51816,9 +52407,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -51826,6 +52419,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -51842,10 +52436,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\mericles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52299B3B-D586-42D6-AC5C-61458EDBFEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B095CBA-1249-4276-AF66-7540E16DD5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -613,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -689,7 +689,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>37</v>
       </c>
@@ -827,7 +827,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2"/>
@@ -907,7 +907,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>37</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="2"/>
@@ -1431,7 +1431,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H32" s="2"/>
       <c r="I32" s="1"/>
       <c r="J32" s="2"/>
@@ -1679,7 +1679,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>37</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>37</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>37</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>37</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>37</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>37</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>37</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>37</v>
       </c>
@@ -5357,7 +5357,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>37</v>
       </c>
@@ -5514,7 +5514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>37</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>37</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>37</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>37</v>
       </c>
@@ -9793,7 +9793,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>37</v>
       </c>
@@ -10121,7 +10121,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>37</v>
       </c>
@@ -10179,7 +10179,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>37</v>
       </c>
@@ -10685,7 +10685,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>37</v>
       </c>
@@ -10746,7 +10746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>37</v>
       </c>
@@ -11225,7 +11225,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>37</v>
       </c>
@@ -11533,7 +11533,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>37</v>
       </c>
@@ -12849,7 +12849,7 @@
         <v>46028.718634259261</v>
       </c>
       <c r="J424" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K424" s="1" t="s">
         <v>11</v>
@@ -12942,7 +12942,7 @@
         <v>46028.720023148147</v>
       </c>
       <c r="J427" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K427" s="1" t="s">
         <v>11</v>
@@ -13003,7 +13003,7 @@
         <v>46028.720717592594</v>
       </c>
       <c r="J429" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K429" s="1" t="s">
         <v>11</v>
@@ -13107,7 +13107,7 @@
         <v>46028.72210648148</v>
       </c>
       <c r="J433" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K433" s="1" t="s">
         <v>11</v>
@@ -13139,7 +13139,7 @@
         <v>46028.722800925927</v>
       </c>
       <c r="J434" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K434" s="1" t="s">
         <v>11</v>
@@ -13171,7 +13171,7 @@
         <v>46028.722800925927</v>
       </c>
       <c r="J435" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K435" s="1" t="s">
         <v>11</v>
@@ -13203,7 +13203,7 @@
         <v>46028.723495370374</v>
       </c>
       <c r="J436" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K436" s="1" t="s">
         <v>11</v>
@@ -13235,7 +13235,7 @@
         <v>46028.724189814813</v>
       </c>
       <c r="J437" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K437" s="1" t="s">
         <v>11</v>
@@ -16176,13 +16176,13 @@
         <v>12</v>
       </c>
       <c r="H535" s="2">
-        <v>1.1574074074074073E-5</v>
+        <v>7.291666666666667E-4</v>
       </c>
       <c r="I535" s="1">
         <v>46237.813425925924</v>
       </c>
       <c r="J535" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K535" s="1" t="s">
         <v>11</v>
@@ -16306,16 +16306,16 @@
         <v>31</v>
       </c>
       <c r="G540" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H540" s="2">
-        <v>0</v>
+        <v>7.9398148148148145E-3</v>
       </c>
       <c r="I540" s="1">
         <v>46237.815509259257</v>
       </c>
       <c r="J540" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K540" s="1" t="s">
         <v>11</v>
@@ -16379,7 +16379,7 @@
         <v>46237.816203703704</v>
       </c>
       <c r="J542" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K542" s="1" t="s">
         <v>11</v>
@@ -16411,7 +16411,7 @@
         <v>46237.81689814815</v>
       </c>
       <c r="J543" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K543" s="1" t="s">
         <v>11</v>
@@ -16443,7 +16443,7 @@
         <v>46237.81759259259</v>
       </c>
       <c r="J544" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K544" s="1" t="s">
         <v>11</v>
@@ -16466,16 +16466,16 @@
         <v>31</v>
       </c>
       <c r="G545" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H545" s="2">
-        <v>0</v>
+        <v>5.9027777777777776E-3</v>
       </c>
       <c r="I545" s="1">
         <v>46237.79409722222</v>
       </c>
       <c r="J545" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K545" s="1" t="s">
         <v>11</v>
@@ -16539,7 +16539,7 @@
         <v>46237.795486111114</v>
       </c>
       <c r="J547" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K547" s="1" t="s">
         <v>11</v>
@@ -54528,6 +54528,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -54820,6 +54821,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -55130,6 +55133,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -55254,6 +55258,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -55265,6 +55270,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -55413,6 +55419,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -55423,10 +55430,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -55460,15 +55469,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -55509,18 +55521,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -55536,6 +55552,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -55545,10 +55562,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -55584,10 +55603,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -55613,6 +55634,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -55627,6 +55649,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -55661,6 +55684,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -55670,6 +55694,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -55679,6 +55704,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -55693,15 +55719,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -55731,6 +55758,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -55751,11 +55779,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -55764,6 +55794,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -55793,6 +55824,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -55802,10 +55834,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -55820,14 +55854,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -55847,10 +55884,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -55870,9 +55909,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -55907,18 +55949,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -55933,12 +55979,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -55953,10 +55999,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -55976,6 +56024,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -55995,6 +56044,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -56004,6 +56054,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -56049,6 +56100,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -56058,6 +56110,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -56072,6 +56125,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -56081,10 +56135,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -56099,6 +56155,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -56108,6 +56165,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -56127,6 +56185,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -56146,10 +56205,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -56159,6 +56220,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -56169,10 +56231,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -56187,18 +56251,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -56218,10 +56286,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -56241,6 +56311,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -56271,7 +56342,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -56286,10 +56356,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -56304,6 +56376,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -56318,11 +56391,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -56332,6 +56405,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -56347,6 +56421,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -56361,6 +56436,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -56381,6 +56457,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -56406,11 +56483,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -56429,15 +56508,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -56447,6 +56527,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -56466,6 +56547,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -56480,6 +56562,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -56499,10 +56582,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -56512,6 +56597,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -56522,6 +56608,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -56558,7 +56645,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -56567,6 +56653,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -56580,10 +56667,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\mericles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B095CBA-1249-4276-AF66-7540E16DD5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{288FF45E-4586-4BB8-9D6E-92E9C5EAA0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -613,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -689,7 +689,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>37</v>
       </c>
@@ -827,7 +827,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2"/>
@@ -907,7 +907,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>37</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H26" s="2"/>
       <c r="I26" s="1"/>
       <c r="J26" s="2"/>
@@ -1431,7 +1431,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H32" s="2"/>
       <c r="I32" s="1"/>
       <c r="J32" s="2"/>
@@ -1679,7 +1679,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>37</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>37</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>37</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>37</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>37</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>37</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>37</v>
       </c>
@@ -3949,7 +3949,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>37</v>
       </c>
@@ -5357,7 +5357,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>37</v>
       </c>
@@ -5514,7 +5514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>37</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>37</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>37</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>37</v>
       </c>
@@ -9793,7 +9793,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="325" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B325" t="s">
         <v>37</v>
       </c>
@@ -10121,7 +10121,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="336" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B336" t="s">
         <v>37</v>
       </c>
@@ -10179,7 +10179,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B338" t="s">
         <v>37</v>
       </c>
@@ -10685,7 +10685,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="354" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>37</v>
       </c>
@@ -10746,7 +10746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="356" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B356" t="s">
         <v>37</v>
       </c>
@@ -11225,7 +11225,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="372" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B372" t="s">
         <v>37</v>
       </c>
@@ -11533,7 +11533,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B382" t="s">
         <v>37</v>
       </c>
@@ -16370,10 +16370,10 @@
         <v>31</v>
       </c>
       <c r="G542" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H542" s="2">
-        <v>0</v>
+        <v>6.4120370370370373E-3</v>
       </c>
       <c r="I542" s="1">
         <v>46237.816203703704</v>
@@ -54528,7 +54528,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -54821,8 +54820,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -55133,7 +55130,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -55258,7 +55254,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -55270,7 +55265,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -55419,35 +55413,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -55458,44 +55446,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -55506,37 +55485,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -55547,52 +55519,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -55603,17 +55565,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -55624,32 +55583,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -55659,106 +55612,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -55768,7 +55701,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -55779,127 +55711,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -55909,62 +55815,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -55984,67 +55877,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -56054,38 +55934,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -56100,117 +55973,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -56219,99 +56069,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -56321,23 +56152,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -56346,52 +56173,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -56405,38 +56222,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -56446,7 +56256,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -56457,23 +56266,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -56483,37 +56288,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -56522,72 +56320,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -56597,76 +56381,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\mericles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{288FF45E-4586-4BB8-9D6E-92E9C5EAA0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFFB90FF-0E43-427B-9255-1F93220DA4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2919" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2918" uniqueCount="67">
   <si>
     <t>Company Name</t>
   </si>
@@ -613,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7400"/>
+  <dimension ref="A1:K7401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -16173,10 +16173,10 @@
         <v>31</v>
       </c>
       <c r="G535" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H535" s="2">
-        <v>7.291666666666667E-4</v>
+        <v>8.4490740740740741E-3</v>
       </c>
       <c r="I535" s="1">
         <v>46237.813425925924</v>
@@ -16189,11 +16189,35 @@
       </c>
     </row>
     <row r="536" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H536" s="2"/>
-      <c r="I536" s="1"/>
-      <c r="J536" s="2"/>
+      <c r="B536" t="s">
+        <v>37</v>
+      </c>
+      <c r="C536">
+        <v>3789</v>
+      </c>
+      <c r="D536" t="s">
+        <v>64</v>
+      </c>
+      <c r="E536" t="s">
+        <v>43</v>
+      </c>
+      <c r="F536" t="s">
+        <v>31</v>
+      </c>
+      <c r="G536" t="s">
+        <v>10</v>
+      </c>
+      <c r="H536" s="2">
+        <v>5.8333333333333336E-3</v>
+      </c>
+      <c r="I536" s="1">
+        <v>46237.814120370371</v>
+      </c>
+      <c r="J536" s="2">
+        <v>0</v>
+      </c>
       <c r="K536" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="537" spans="2:11" x14ac:dyDescent="0.25">
@@ -16201,10 +16225,10 @@
         <v>37</v>
       </c>
       <c r="C537">
-        <v>3789</v>
+        <v>1932</v>
       </c>
       <c r="D537" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E537" t="s">
         <v>43</v>
@@ -16216,7 +16240,7 @@
         <v>10</v>
       </c>
       <c r="H537" s="2">
-        <v>5.8333333333333336E-3</v>
+        <v>8.2291666666666659E-3</v>
       </c>
       <c r="I537" s="1">
         <v>46237.814120370371</v>
@@ -16233,10 +16257,10 @@
         <v>37</v>
       </c>
       <c r="C538">
-        <v>1932</v>
+        <v>1935</v>
       </c>
       <c r="D538" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E538" t="s">
         <v>43</v>
@@ -16248,10 +16272,10 @@
         <v>10</v>
       </c>
       <c r="H538" s="2">
-        <v>8.2291666666666659E-3</v>
+        <v>5.364583333333333E-2</v>
       </c>
       <c r="I538" s="1">
-        <v>46237.814120370371</v>
+        <v>46237.814814814818</v>
       </c>
       <c r="J538" s="2">
         <v>0</v>
@@ -16265,13 +16289,10 @@
         <v>37</v>
       </c>
       <c r="C539">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="D539" t="s">
-        <v>49</v>
-      </c>
-      <c r="E539" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F539" t="s">
         <v>31</v>
@@ -16280,13 +16301,13 @@
         <v>10</v>
       </c>
       <c r="H539" s="2">
-        <v>5.364583333333333E-2</v>
+        <v>7.9398148148148145E-3</v>
       </c>
       <c r="I539" s="1">
-        <v>46237.814814814818</v>
+        <v>46237.815509259257</v>
       </c>
       <c r="J539" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K539" s="1" t="s">
         <v>11</v>
@@ -16297,10 +16318,13 @@
         <v>37</v>
       </c>
       <c r="C540">
-        <v>1936</v>
+        <v>3890</v>
       </c>
       <c r="D540" t="s">
-        <v>50</v>
+        <v>66</v>
+      </c>
+      <c r="E540" t="s">
+        <v>43</v>
       </c>
       <c r="F540" t="s">
         <v>31</v>
@@ -16309,13 +16333,13 @@
         <v>10</v>
       </c>
       <c r="H540" s="2">
-        <v>7.9398148148148145E-3</v>
+        <v>5.8333333333333336E-3</v>
       </c>
       <c r="I540" s="1">
-        <v>46237.815509259257</v>
+        <v>46237.816203703704</v>
       </c>
       <c r="J540" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K540" s="1" t="s">
         <v>11</v>
@@ -16326,10 +16350,10 @@
         <v>37</v>
       </c>
       <c r="C541">
-        <v>3890</v>
+        <v>1937</v>
       </c>
       <c r="D541" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="E541" t="s">
         <v>43</v>
@@ -16341,13 +16365,13 @@
         <v>10</v>
       </c>
       <c r="H541" s="2">
-        <v>5.8333333333333336E-3</v>
+        <v>6.4120370370370373E-3</v>
       </c>
       <c r="I541" s="1">
         <v>46237.816203703704</v>
       </c>
       <c r="J541" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K541" s="1" t="s">
         <v>11</v>
@@ -16358,10 +16382,10 @@
         <v>37</v>
       </c>
       <c r="C542">
-        <v>1937</v>
+        <v>3788</v>
       </c>
       <c r="D542" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E542" t="s">
         <v>43</v>
@@ -16373,10 +16397,10 @@
         <v>10</v>
       </c>
       <c r="H542" s="2">
-        <v>6.4120370370370373E-3</v>
+        <v>9.7916666666666673E-3</v>
       </c>
       <c r="I542" s="1">
-        <v>46237.816203703704</v>
+        <v>46237.81689814815</v>
       </c>
       <c r="J542" s="2">
         <v>3</v>
@@ -16390,10 +16414,10 @@
         <v>37</v>
       </c>
       <c r="C543">
-        <v>3788</v>
+        <v>3868</v>
       </c>
       <c r="D543" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E543" t="s">
         <v>43</v>
@@ -16408,7 +16432,7 @@
         <v>0</v>
       </c>
       <c r="I543" s="1">
-        <v>46237.81689814815</v>
+        <v>46237.81759259259</v>
       </c>
       <c r="J543" s="2">
         <v>3</v>
@@ -16422,10 +16446,10 @@
         <v>37</v>
       </c>
       <c r="C544">
-        <v>3868</v>
+        <v>1939</v>
       </c>
       <c r="D544" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E544" t="s">
         <v>43</v>
@@ -16434,16 +16458,16 @@
         <v>31</v>
       </c>
       <c r="G544" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H544" s="2">
-        <v>0</v>
+        <v>5.9027777777777776E-3</v>
       </c>
       <c r="I544" s="1">
-        <v>46237.81759259259</v>
+        <v>46237.79409722222</v>
       </c>
       <c r="J544" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K544" s="1" t="s">
         <v>11</v>
@@ -16454,10 +16478,10 @@
         <v>37</v>
       </c>
       <c r="C545">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="D545" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E545" t="s">
         <v>43</v>
@@ -16469,13 +16493,13 @@
         <v>10</v>
       </c>
       <c r="H545" s="2">
-        <v>5.9027777777777776E-3</v>
+        <v>7.6157407407407406E-3</v>
       </c>
       <c r="I545" s="1">
-        <v>46237.79409722222</v>
+        <v>46237.794791666667</v>
       </c>
       <c r="J545" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K545" s="1" t="s">
         <v>11</v>
@@ -16486,10 +16510,10 @@
         <v>37</v>
       </c>
       <c r="C546">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="D546" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E546" t="s">
         <v>43</v>
@@ -16498,16 +16522,16 @@
         <v>31</v>
       </c>
       <c r="G546" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H546" s="2">
-        <v>7.6157407407407406E-3</v>
+        <v>0</v>
       </c>
       <c r="I546" s="1">
-        <v>46237.794791666667</v>
+        <v>46237.795486111114</v>
       </c>
       <c r="J546" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K546" s="1" t="s">
         <v>11</v>
@@ -16518,10 +16542,10 @@
         <v>37</v>
       </c>
       <c r="C547">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="D547" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E547" t="s">
         <v>43</v>
@@ -16530,52 +16554,26 @@
         <v>31</v>
       </c>
       <c r="G547" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H547" s="2">
-        <v>0</v>
+        <v>7.2453703703703708E-3</v>
       </c>
       <c r="I547" s="1">
         <v>46237.795486111114</v>
       </c>
       <c r="J547" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K547" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="548" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B548" t="s">
-        <v>37</v>
-      </c>
-      <c r="C548">
-        <v>1944</v>
-      </c>
-      <c r="D548" t="s">
-        <v>58</v>
-      </c>
-      <c r="E548" t="s">
-        <v>43</v>
-      </c>
-      <c r="F548" t="s">
-        <v>31</v>
-      </c>
-      <c r="G548" t="s">
-        <v>10</v>
-      </c>
-      <c r="H548" s="2">
-        <v>7.2453703703703708E-3</v>
-      </c>
-      <c r="I548" s="1">
-        <v>46237.795486111114</v>
-      </c>
-      <c r="J548" s="2">
-        <v>0</v>
-      </c>
-      <c r="K548" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="H548" s="2"/>
+      <c r="I548" s="1"/>
+      <c r="J548" s="2"/>
+      <c r="K548" s="1"/>
     </row>
     <row r="549" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H549" s="2"/>
@@ -54528,6 +54526,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -54820,6 +54819,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -55130,6 +55131,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -55254,6 +55256,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -55265,6 +55268,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -55413,29 +55417,35 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -55446,35 +55456,44 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -55485,30 +55504,37 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -55519,42 +55545,52 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -55565,14 +55601,17 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -55583,26 +55622,32 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -55612,86 +55657,107 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -55701,6 +55767,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -55711,101 +55778,127 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -55815,49 +55908,62 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -55872,59 +55978,73 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -55934,31 +56054,38 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -55968,99 +56095,123 @@
       <c r="K7287" s="1"/>
     </row>
     <row r="7288" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7288" s="2"/>
       <c r="I7288" s="1"/>
       <c r="J7288" s="2"/>
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -56069,80 +56220,99 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -56152,67 +56322,83 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -56222,31 +56408,38 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -56256,6 +56449,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -56266,19 +56460,23 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -56288,90 +56486,112 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -56381,51 +56601,71 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7394" s="2"/>
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7398" s="2"/>
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
